--- a/display/SimOutput_v2.xlsx
+++ b/display/SimOutput_v2.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M276"/>
+  <dimension ref="A1:O276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -517,10 +517,10 @@
     <col width="30" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
     <col width="9" customWidth="1" min="12" max="12"/>
     <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2019,14 +2019,15 @@
       <c r="G55" s="6" t="n"/>
       <c r="H55" s="6" t="n"/>
       <c r="I55" s="6" t="n"/>
-      <c r="J55" s="5" t="inlineStr">
+      <c r="J55" s="6" t="n"/>
+      <c r="L55" s="5" t="inlineStr">
         <is>
           <t>PACKS RESULT</t>
         </is>
       </c>
-      <c r="K55" s="6" t="n"/>
-      <c r="L55" s="6" t="n"/>
       <c r="M55" s="6" t="n"/>
+      <c r="N55" s="6" t="n"/>
+      <c r="O55" s="6" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
@@ -2046,35 +2047,40 @@
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
+          <t>Earned From</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
           <t>Album</t>
         </is>
       </c>
-      <c r="E56" s="7" t="inlineStr">
+      <c r="F56" s="7" t="inlineStr">
         <is>
           <t>Cards Drawn</t>
         </is>
       </c>
-      <c r="F56" s="7" t="inlineStr">
+      <c r="G56" s="7" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="G56" s="7" t="inlineStr">
+      <c r="H56" s="7" t="inlineStr">
         <is>
           <t>Dupes</t>
         </is>
       </c>
-      <c r="H56" s="7" t="inlineStr">
+      <c r="I56" s="7" t="inlineStr">
         <is>
           <t>Stars Balance</t>
         </is>
       </c>
-      <c r="I56" s="7" t="inlineStr">
+      <c r="J56" s="7" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="J56" s="2" t="inlineStr">
+      <c r="L56" s="2" t="inlineStr">
         <is>
           <t>Album #1</t>
         </is>
@@ -2090,7 +2096,8 @@
       <c r="G57" s="11" t="n"/>
       <c r="H57" s="11" t="n"/>
       <c r="I57" s="11" t="n"/>
-      <c r="J57" s="12" t="inlineStr">
+      <c r="J57" s="11" t="n"/>
+      <c r="L57" s="12" t="inlineStr">
         <is>
           <t>Set #1</t>
         </is>
@@ -2106,9 +2113,10 @@
       <c r="G58" s="11" t="n"/>
       <c r="H58" s="11" t="n"/>
       <c r="I58" s="11" t="n"/>
-      <c r="J58" s="13" t="n"/>
-      <c r="K58" s="13" t="n"/>
+      <c r="J58" s="11" t="n"/>
       <c r="L58" s="13" t="n"/>
+      <c r="M58" s="13" t="n"/>
+      <c r="N58" s="13" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="11" t="n"/>
@@ -2120,9 +2128,10 @@
       <c r="G59" s="11" t="n"/>
       <c r="H59" s="11" t="n"/>
       <c r="I59" s="11" t="n"/>
-      <c r="J59" s="13" t="n"/>
-      <c r="K59" s="13" t="n"/>
+      <c r="J59" s="11" t="n"/>
       <c r="L59" s="13" t="n"/>
+      <c r="M59" s="13" t="n"/>
+      <c r="N59" s="13" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="11" t="n"/>
@@ -2134,9 +2143,10 @@
       <c r="G60" s="11" t="n"/>
       <c r="H60" s="11" t="n"/>
       <c r="I60" s="11" t="n"/>
-      <c r="J60" s="13" t="n"/>
-      <c r="K60" s="13" t="n"/>
+      <c r="J60" s="11" t="n"/>
       <c r="L60" s="13" t="n"/>
+      <c r="M60" s="13" t="n"/>
+      <c r="N60" s="13" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="11" t="n"/>
@@ -2148,7 +2158,8 @@
       <c r="G61" s="11" t="n"/>
       <c r="H61" s="11" t="n"/>
       <c r="I61" s="11" t="n"/>
-      <c r="J61" s="12" t="inlineStr">
+      <c r="J61" s="11" t="n"/>
+      <c r="L61" s="12" t="inlineStr">
         <is>
           <t>Set #2</t>
         </is>
@@ -2164,9 +2175,10 @@
       <c r="G62" s="11" t="n"/>
       <c r="H62" s="11" t="n"/>
       <c r="I62" s="11" t="n"/>
-      <c r="J62" s="13" t="n"/>
-      <c r="K62" s="13" t="n"/>
+      <c r="J62" s="11" t="n"/>
       <c r="L62" s="13" t="n"/>
+      <c r="M62" s="13" t="n"/>
+      <c r="N62" s="13" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="11" t="n"/>
@@ -2178,9 +2190,10 @@
       <c r="G63" s="11" t="n"/>
       <c r="H63" s="11" t="n"/>
       <c r="I63" s="11" t="n"/>
-      <c r="J63" s="13" t="n"/>
-      <c r="K63" s="13" t="n"/>
+      <c r="J63" s="11" t="n"/>
       <c r="L63" s="13" t="n"/>
+      <c r="M63" s="13" t="n"/>
+      <c r="N63" s="13" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="11" t="n"/>
@@ -2192,9 +2205,10 @@
       <c r="G64" s="11" t="n"/>
       <c r="H64" s="11" t="n"/>
       <c r="I64" s="11" t="n"/>
-      <c r="J64" s="13" t="n"/>
-      <c r="K64" s="13" t="n"/>
+      <c r="J64" s="11" t="n"/>
       <c r="L64" s="13" t="n"/>
+      <c r="M64" s="13" t="n"/>
+      <c r="N64" s="13" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="11" t="n"/>
@@ -2206,7 +2220,8 @@
       <c r="G65" s="11" t="n"/>
       <c r="H65" s="11" t="n"/>
       <c r="I65" s="11" t="n"/>
-      <c r="J65" s="12" t="inlineStr">
+      <c r="J65" s="11" t="n"/>
+      <c r="L65" s="12" t="inlineStr">
         <is>
           <t>Set #3</t>
         </is>
@@ -2222,9 +2237,10 @@
       <c r="G66" s="11" t="n"/>
       <c r="H66" s="11" t="n"/>
       <c r="I66" s="11" t="n"/>
-      <c r="J66" s="13" t="n"/>
-      <c r="K66" s="13" t="n"/>
+      <c r="J66" s="11" t="n"/>
       <c r="L66" s="13" t="n"/>
+      <c r="M66" s="13" t="n"/>
+      <c r="N66" s="13" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="11" t="n"/>
@@ -2236,9 +2252,10 @@
       <c r="G67" s="11" t="n"/>
       <c r="H67" s="11" t="n"/>
       <c r="I67" s="11" t="n"/>
-      <c r="J67" s="13" t="n"/>
-      <c r="K67" s="13" t="n"/>
+      <c r="J67" s="11" t="n"/>
       <c r="L67" s="13" t="n"/>
+      <c r="M67" s="13" t="n"/>
+      <c r="N67" s="13" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="11" t="n"/>
@@ -2250,9 +2267,10 @@
       <c r="G68" s="11" t="n"/>
       <c r="H68" s="11" t="n"/>
       <c r="I68" s="11" t="n"/>
-      <c r="J68" s="13" t="n"/>
-      <c r="K68" s="13" t="n"/>
+      <c r="J68" s="11" t="n"/>
       <c r="L68" s="13" t="n"/>
+      <c r="M68" s="13" t="n"/>
+      <c r="N68" s="13" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="11" t="n"/>
@@ -2264,7 +2282,8 @@
       <c r="G69" s="11" t="n"/>
       <c r="H69" s="11" t="n"/>
       <c r="I69" s="11" t="n"/>
-      <c r="J69" s="12" t="inlineStr">
+      <c r="J69" s="11" t="n"/>
+      <c r="L69" s="12" t="inlineStr">
         <is>
           <t>Set #4</t>
         </is>
@@ -2280,9 +2299,10 @@
       <c r="G70" s="11" t="n"/>
       <c r="H70" s="11" t="n"/>
       <c r="I70" s="11" t="n"/>
-      <c r="J70" s="13" t="n"/>
-      <c r="K70" s="13" t="n"/>
+      <c r="J70" s="11" t="n"/>
       <c r="L70" s="13" t="n"/>
+      <c r="M70" s="13" t="n"/>
+      <c r="N70" s="13" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="11" t="n"/>
@@ -2294,9 +2314,10 @@
       <c r="G71" s="11" t="n"/>
       <c r="H71" s="11" t="n"/>
       <c r="I71" s="11" t="n"/>
-      <c r="J71" s="13" t="n"/>
-      <c r="K71" s="13" t="n"/>
+      <c r="J71" s="11" t="n"/>
       <c r="L71" s="13" t="n"/>
+      <c r="M71" s="13" t="n"/>
+      <c r="N71" s="13" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="11" t="n"/>
@@ -2308,9 +2329,10 @@
       <c r="G72" s="11" t="n"/>
       <c r="H72" s="11" t="n"/>
       <c r="I72" s="11" t="n"/>
-      <c r="J72" s="13" t="n"/>
-      <c r="K72" s="13" t="n"/>
+      <c r="J72" s="11" t="n"/>
       <c r="L72" s="13" t="n"/>
+      <c r="M72" s="13" t="n"/>
+      <c r="N72" s="13" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="11" t="n"/>
@@ -2322,7 +2344,8 @@
       <c r="G73" s="11" t="n"/>
       <c r="H73" s="11" t="n"/>
       <c r="I73" s="11" t="n"/>
-      <c r="J73" s="12" t="inlineStr">
+      <c r="J73" s="11" t="n"/>
+      <c r="L73" s="12" t="inlineStr">
         <is>
           <t>Set #5</t>
         </is>
@@ -2338,9 +2361,10 @@
       <c r="G74" s="11" t="n"/>
       <c r="H74" s="11" t="n"/>
       <c r="I74" s="11" t="n"/>
-      <c r="J74" s="13" t="n"/>
-      <c r="K74" s="13" t="n"/>
+      <c r="J74" s="11" t="n"/>
       <c r="L74" s="13" t="n"/>
+      <c r="M74" s="13" t="n"/>
+      <c r="N74" s="13" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="11" t="n"/>
@@ -2352,9 +2376,10 @@
       <c r="G75" s="11" t="n"/>
       <c r="H75" s="11" t="n"/>
       <c r="I75" s="11" t="n"/>
-      <c r="J75" s="13" t="n"/>
-      <c r="K75" s="13" t="n"/>
+      <c r="J75" s="11" t="n"/>
       <c r="L75" s="13" t="n"/>
+      <c r="M75" s="13" t="n"/>
+      <c r="N75" s="13" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="11" t="n"/>
@@ -2366,9 +2391,10 @@
       <c r="G76" s="11" t="n"/>
       <c r="H76" s="11" t="n"/>
       <c r="I76" s="11" t="n"/>
-      <c r="J76" s="13" t="n"/>
-      <c r="K76" s="13" t="n"/>
+      <c r="J76" s="11" t="n"/>
       <c r="L76" s="13" t="n"/>
+      <c r="M76" s="13" t="n"/>
+      <c r="N76" s="13" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="11" t="n"/>
@@ -2380,7 +2406,8 @@
       <c r="G77" s="11" t="n"/>
       <c r="H77" s="11" t="n"/>
       <c r="I77" s="11" t="n"/>
-      <c r="J77" s="12" t="inlineStr">
+      <c r="J77" s="11" t="n"/>
+      <c r="L77" s="12" t="inlineStr">
         <is>
           <t>Set #6</t>
         </is>
@@ -2396,9 +2423,10 @@
       <c r="G78" s="11" t="n"/>
       <c r="H78" s="11" t="n"/>
       <c r="I78" s="11" t="n"/>
-      <c r="J78" s="13" t="n"/>
-      <c r="K78" s="13" t="n"/>
+      <c r="J78" s="11" t="n"/>
       <c r="L78" s="13" t="n"/>
+      <c r="M78" s="13" t="n"/>
+      <c r="N78" s="13" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="11" t="n"/>
@@ -2410,9 +2438,10 @@
       <c r="G79" s="11" t="n"/>
       <c r="H79" s="11" t="n"/>
       <c r="I79" s="11" t="n"/>
-      <c r="J79" s="13" t="n"/>
-      <c r="K79" s="13" t="n"/>
+      <c r="J79" s="11" t="n"/>
       <c r="L79" s="13" t="n"/>
+      <c r="M79" s="13" t="n"/>
+      <c r="N79" s="13" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="11" t="n"/>
@@ -2424,9 +2453,10 @@
       <c r="G80" s="11" t="n"/>
       <c r="H80" s="11" t="n"/>
       <c r="I80" s="11" t="n"/>
-      <c r="J80" s="13" t="n"/>
-      <c r="K80" s="13" t="n"/>
+      <c r="J80" s="11" t="n"/>
       <c r="L80" s="13" t="n"/>
+      <c r="M80" s="13" t="n"/>
+      <c r="N80" s="13" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="11" t="n"/>
@@ -2438,7 +2468,8 @@
       <c r="G81" s="11" t="n"/>
       <c r="H81" s="11" t="n"/>
       <c r="I81" s="11" t="n"/>
-      <c r="J81" s="12" t="inlineStr">
+      <c r="J81" s="11" t="n"/>
+      <c r="L81" s="12" t="inlineStr">
         <is>
           <t>Set #7</t>
         </is>
@@ -2454,9 +2485,10 @@
       <c r="G82" s="11" t="n"/>
       <c r="H82" s="11" t="n"/>
       <c r="I82" s="11" t="n"/>
-      <c r="J82" s="13" t="n"/>
-      <c r="K82" s="13" t="n"/>
+      <c r="J82" s="11" t="n"/>
       <c r="L82" s="13" t="n"/>
+      <c r="M82" s="13" t="n"/>
+      <c r="N82" s="13" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="11" t="n"/>
@@ -2468,9 +2500,10 @@
       <c r="G83" s="11" t="n"/>
       <c r="H83" s="11" t="n"/>
       <c r="I83" s="11" t="n"/>
-      <c r="J83" s="13" t="n"/>
-      <c r="K83" s="13" t="n"/>
+      <c r="J83" s="11" t="n"/>
       <c r="L83" s="13" t="n"/>
+      <c r="M83" s="13" t="n"/>
+      <c r="N83" s="13" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="11" t="n"/>
@@ -2482,9 +2515,10 @@
       <c r="G84" s="11" t="n"/>
       <c r="H84" s="11" t="n"/>
       <c r="I84" s="11" t="n"/>
-      <c r="J84" s="13" t="n"/>
-      <c r="K84" s="13" t="n"/>
+      <c r="J84" s="11" t="n"/>
       <c r="L84" s="13" t="n"/>
+      <c r="M84" s="13" t="n"/>
+      <c r="N84" s="13" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="11" t="n"/>
@@ -2496,7 +2530,8 @@
       <c r="G85" s="11" t="n"/>
       <c r="H85" s="11" t="n"/>
       <c r="I85" s="11" t="n"/>
-      <c r="J85" s="12" t="inlineStr">
+      <c r="J85" s="11" t="n"/>
+      <c r="L85" s="12" t="inlineStr">
         <is>
           <t>Set #8</t>
         </is>
@@ -2512,9 +2547,10 @@
       <c r="G86" s="11" t="n"/>
       <c r="H86" s="11" t="n"/>
       <c r="I86" s="11" t="n"/>
-      <c r="J86" s="13" t="n"/>
-      <c r="K86" s="13" t="n"/>
+      <c r="J86" s="11" t="n"/>
       <c r="L86" s="13" t="n"/>
+      <c r="M86" s="13" t="n"/>
+      <c r="N86" s="13" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="11" t="n"/>
@@ -2526,9 +2562,10 @@
       <c r="G87" s="11" t="n"/>
       <c r="H87" s="11" t="n"/>
       <c r="I87" s="11" t="n"/>
-      <c r="J87" s="13" t="n"/>
-      <c r="K87" s="13" t="n"/>
+      <c r="J87" s="11" t="n"/>
       <c r="L87" s="13" t="n"/>
+      <c r="M87" s="13" t="n"/>
+      <c r="N87" s="13" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="11" t="n"/>
@@ -2540,9 +2577,10 @@
       <c r="G88" s="11" t="n"/>
       <c r="H88" s="11" t="n"/>
       <c r="I88" s="11" t="n"/>
-      <c r="J88" s="13" t="n"/>
-      <c r="K88" s="13" t="n"/>
+      <c r="J88" s="11" t="n"/>
       <c r="L88" s="13" t="n"/>
+      <c r="M88" s="13" t="n"/>
+      <c r="N88" s="13" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="11" t="n"/>
@@ -2554,6 +2592,7 @@
       <c r="G89" s="11" t="n"/>
       <c r="H89" s="11" t="n"/>
       <c r="I89" s="11" t="n"/>
+      <c r="J89" s="11" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="11" t="n"/>
@@ -2565,7 +2604,8 @@
       <c r="G90" s="11" t="n"/>
       <c r="H90" s="11" t="n"/>
       <c r="I90" s="11" t="n"/>
-      <c r="J90" s="2" t="inlineStr">
+      <c r="J90" s="11" t="n"/>
+      <c r="L90" s="2" t="inlineStr">
         <is>
           <t>Album #2</t>
         </is>
@@ -2581,7 +2621,8 @@
       <c r="G91" s="11" t="n"/>
       <c r="H91" s="11" t="n"/>
       <c r="I91" s="11" t="n"/>
-      <c r="J91" s="12" t="inlineStr">
+      <c r="J91" s="11" t="n"/>
+      <c r="L91" s="12" t="inlineStr">
         <is>
           <t>Set #1</t>
         </is>
@@ -2597,9 +2638,10 @@
       <c r="G92" s="11" t="n"/>
       <c r="H92" s="11" t="n"/>
       <c r="I92" s="11" t="n"/>
-      <c r="J92" s="13" t="n"/>
-      <c r="K92" s="13" t="n"/>
+      <c r="J92" s="11" t="n"/>
       <c r="L92" s="13" t="n"/>
+      <c r="M92" s="13" t="n"/>
+      <c r="N92" s="13" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="11" t="n"/>
@@ -2611,9 +2653,10 @@
       <c r="G93" s="11" t="n"/>
       <c r="H93" s="11" t="n"/>
       <c r="I93" s="11" t="n"/>
-      <c r="J93" s="13" t="n"/>
-      <c r="K93" s="13" t="n"/>
+      <c r="J93" s="11" t="n"/>
       <c r="L93" s="13" t="n"/>
+      <c r="M93" s="13" t="n"/>
+      <c r="N93" s="13" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="11" t="n"/>
@@ -2625,9 +2668,10 @@
       <c r="G94" s="11" t="n"/>
       <c r="H94" s="11" t="n"/>
       <c r="I94" s="11" t="n"/>
-      <c r="J94" s="13" t="n"/>
-      <c r="K94" s="13" t="n"/>
+      <c r="J94" s="11" t="n"/>
       <c r="L94" s="13" t="n"/>
+      <c r="M94" s="13" t="n"/>
+      <c r="N94" s="13" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="11" t="n"/>
@@ -2639,7 +2683,8 @@
       <c r="G95" s="11" t="n"/>
       <c r="H95" s="11" t="n"/>
       <c r="I95" s="11" t="n"/>
-      <c r="J95" s="12" t="inlineStr">
+      <c r="J95" s="11" t="n"/>
+      <c r="L95" s="12" t="inlineStr">
         <is>
           <t>Set #2</t>
         </is>
@@ -2655,9 +2700,10 @@
       <c r="G96" s="11" t="n"/>
       <c r="H96" s="11" t="n"/>
       <c r="I96" s="11" t="n"/>
-      <c r="J96" s="13" t="n"/>
-      <c r="K96" s="13" t="n"/>
+      <c r="J96" s="11" t="n"/>
       <c r="L96" s="13" t="n"/>
+      <c r="M96" s="13" t="n"/>
+      <c r="N96" s="13" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="11" t="n"/>
@@ -2669,9 +2715,10 @@
       <c r="G97" s="11" t="n"/>
       <c r="H97" s="11" t="n"/>
       <c r="I97" s="11" t="n"/>
-      <c r="J97" s="13" t="n"/>
-      <c r="K97" s="13" t="n"/>
+      <c r="J97" s="11" t="n"/>
       <c r="L97" s="13" t="n"/>
+      <c r="M97" s="13" t="n"/>
+      <c r="N97" s="13" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="11" t="n"/>
@@ -2683,9 +2730,10 @@
       <c r="G98" s="11" t="n"/>
       <c r="H98" s="11" t="n"/>
       <c r="I98" s="11" t="n"/>
-      <c r="J98" s="13" t="n"/>
-      <c r="K98" s="13" t="n"/>
+      <c r="J98" s="11" t="n"/>
       <c r="L98" s="13" t="n"/>
+      <c r="M98" s="13" t="n"/>
+      <c r="N98" s="13" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="11" t="n"/>
@@ -2697,7 +2745,8 @@
       <c r="G99" s="11" t="n"/>
       <c r="H99" s="11" t="n"/>
       <c r="I99" s="11" t="n"/>
-      <c r="J99" s="12" t="inlineStr">
+      <c r="J99" s="11" t="n"/>
+      <c r="L99" s="12" t="inlineStr">
         <is>
           <t>Set #3</t>
         </is>
@@ -2713,9 +2762,10 @@
       <c r="G100" s="11" t="n"/>
       <c r="H100" s="11" t="n"/>
       <c r="I100" s="11" t="n"/>
-      <c r="J100" s="13" t="n"/>
-      <c r="K100" s="13" t="n"/>
+      <c r="J100" s="11" t="n"/>
       <c r="L100" s="13" t="n"/>
+      <c r="M100" s="13" t="n"/>
+      <c r="N100" s="13" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="11" t="n"/>
@@ -2727,9 +2777,10 @@
       <c r="G101" s="11" t="n"/>
       <c r="H101" s="11" t="n"/>
       <c r="I101" s="11" t="n"/>
-      <c r="J101" s="13" t="n"/>
-      <c r="K101" s="13" t="n"/>
+      <c r="J101" s="11" t="n"/>
       <c r="L101" s="13" t="n"/>
+      <c r="M101" s="13" t="n"/>
+      <c r="N101" s="13" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="11" t="n"/>
@@ -2741,9 +2792,10 @@
       <c r="G102" s="11" t="n"/>
       <c r="H102" s="11" t="n"/>
       <c r="I102" s="11" t="n"/>
-      <c r="J102" s="13" t="n"/>
-      <c r="K102" s="13" t="n"/>
+      <c r="J102" s="11" t="n"/>
       <c r="L102" s="13" t="n"/>
+      <c r="M102" s="13" t="n"/>
+      <c r="N102" s="13" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="11" t="n"/>
@@ -2755,7 +2807,8 @@
       <c r="G103" s="11" t="n"/>
       <c r="H103" s="11" t="n"/>
       <c r="I103" s="11" t="n"/>
-      <c r="J103" s="12" t="inlineStr">
+      <c r="J103" s="11" t="n"/>
+      <c r="L103" s="12" t="inlineStr">
         <is>
           <t>Set #4</t>
         </is>
@@ -2771,9 +2824,10 @@
       <c r="G104" s="11" t="n"/>
       <c r="H104" s="11" t="n"/>
       <c r="I104" s="11" t="n"/>
-      <c r="J104" s="13" t="n"/>
-      <c r="K104" s="13" t="n"/>
+      <c r="J104" s="11" t="n"/>
       <c r="L104" s="13" t="n"/>
+      <c r="M104" s="13" t="n"/>
+      <c r="N104" s="13" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="11" t="n"/>
@@ -2785,9 +2839,10 @@
       <c r="G105" s="11" t="n"/>
       <c r="H105" s="11" t="n"/>
       <c r="I105" s="11" t="n"/>
-      <c r="J105" s="13" t="n"/>
-      <c r="K105" s="13" t="n"/>
+      <c r="J105" s="11" t="n"/>
       <c r="L105" s="13" t="n"/>
+      <c r="M105" s="13" t="n"/>
+      <c r="N105" s="13" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="11" t="n"/>
@@ -2799,9 +2854,10 @@
       <c r="G106" s="11" t="n"/>
       <c r="H106" s="11" t="n"/>
       <c r="I106" s="11" t="n"/>
-      <c r="J106" s="13" t="n"/>
-      <c r="K106" s="13" t="n"/>
+      <c r="J106" s="11" t="n"/>
       <c r="L106" s="13" t="n"/>
+      <c r="M106" s="13" t="n"/>
+      <c r="N106" s="13" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="11" t="n"/>
@@ -2813,7 +2869,8 @@
       <c r="G107" s="11" t="n"/>
       <c r="H107" s="11" t="n"/>
       <c r="I107" s="11" t="n"/>
-      <c r="J107" s="12" t="inlineStr">
+      <c r="J107" s="11" t="n"/>
+      <c r="L107" s="12" t="inlineStr">
         <is>
           <t>Set #5</t>
         </is>
@@ -2829,9 +2886,10 @@
       <c r="G108" s="11" t="n"/>
       <c r="H108" s="11" t="n"/>
       <c r="I108" s="11" t="n"/>
-      <c r="J108" s="13" t="n"/>
-      <c r="K108" s="13" t="n"/>
+      <c r="J108" s="11" t="n"/>
       <c r="L108" s="13" t="n"/>
+      <c r="M108" s="13" t="n"/>
+      <c r="N108" s="13" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="11" t="n"/>
@@ -2843,9 +2901,10 @@
       <c r="G109" s="11" t="n"/>
       <c r="H109" s="11" t="n"/>
       <c r="I109" s="11" t="n"/>
-      <c r="J109" s="13" t="n"/>
-      <c r="K109" s="13" t="n"/>
+      <c r="J109" s="11" t="n"/>
       <c r="L109" s="13" t="n"/>
+      <c r="M109" s="13" t="n"/>
+      <c r="N109" s="13" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="11" t="n"/>
@@ -2857,9 +2916,10 @@
       <c r="G110" s="11" t="n"/>
       <c r="H110" s="11" t="n"/>
       <c r="I110" s="11" t="n"/>
-      <c r="J110" s="13" t="n"/>
-      <c r="K110" s="13" t="n"/>
+      <c r="J110" s="11" t="n"/>
       <c r="L110" s="13" t="n"/>
+      <c r="M110" s="13" t="n"/>
+      <c r="N110" s="13" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="11" t="n"/>
@@ -2871,7 +2931,8 @@
       <c r="G111" s="11" t="n"/>
       <c r="H111" s="11" t="n"/>
       <c r="I111" s="11" t="n"/>
-      <c r="J111" s="12" t="inlineStr">
+      <c r="J111" s="11" t="n"/>
+      <c r="L111" s="12" t="inlineStr">
         <is>
           <t>Set #6</t>
         </is>
@@ -2887,9 +2948,10 @@
       <c r="G112" s="11" t="n"/>
       <c r="H112" s="11" t="n"/>
       <c r="I112" s="11" t="n"/>
-      <c r="J112" s="13" t="n"/>
-      <c r="K112" s="13" t="n"/>
+      <c r="J112" s="11" t="n"/>
       <c r="L112" s="13" t="n"/>
+      <c r="M112" s="13" t="n"/>
+      <c r="N112" s="13" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="11" t="n"/>
@@ -2901,9 +2963,10 @@
       <c r="G113" s="11" t="n"/>
       <c r="H113" s="11" t="n"/>
       <c r="I113" s="11" t="n"/>
-      <c r="J113" s="13" t="n"/>
-      <c r="K113" s="13" t="n"/>
+      <c r="J113" s="11" t="n"/>
       <c r="L113" s="13" t="n"/>
+      <c r="M113" s="13" t="n"/>
+      <c r="N113" s="13" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="11" t="n"/>
@@ -2915,9 +2978,10 @@
       <c r="G114" s="11" t="n"/>
       <c r="H114" s="11" t="n"/>
       <c r="I114" s="11" t="n"/>
-      <c r="J114" s="13" t="n"/>
-      <c r="K114" s="13" t="n"/>
+      <c r="J114" s="11" t="n"/>
       <c r="L114" s="13" t="n"/>
+      <c r="M114" s="13" t="n"/>
+      <c r="N114" s="13" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="11" t="n"/>
@@ -2929,7 +2993,8 @@
       <c r="G115" s="11" t="n"/>
       <c r="H115" s="11" t="n"/>
       <c r="I115" s="11" t="n"/>
-      <c r="J115" s="12" t="inlineStr">
+      <c r="J115" s="11" t="n"/>
+      <c r="L115" s="12" t="inlineStr">
         <is>
           <t>Set #7</t>
         </is>
@@ -2945,9 +3010,10 @@
       <c r="G116" s="11" t="n"/>
       <c r="H116" s="11" t="n"/>
       <c r="I116" s="11" t="n"/>
-      <c r="J116" s="13" t="n"/>
-      <c r="K116" s="13" t="n"/>
+      <c r="J116" s="11" t="n"/>
       <c r="L116" s="13" t="n"/>
+      <c r="M116" s="13" t="n"/>
+      <c r="N116" s="13" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="11" t="n"/>
@@ -2959,9 +3025,10 @@
       <c r="G117" s="11" t="n"/>
       <c r="H117" s="11" t="n"/>
       <c r="I117" s="11" t="n"/>
-      <c r="J117" s="13" t="n"/>
-      <c r="K117" s="13" t="n"/>
+      <c r="J117" s="11" t="n"/>
       <c r="L117" s="13" t="n"/>
+      <c r="M117" s="13" t="n"/>
+      <c r="N117" s="13" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="11" t="n"/>
@@ -2973,9 +3040,10 @@
       <c r="G118" s="11" t="n"/>
       <c r="H118" s="11" t="n"/>
       <c r="I118" s="11" t="n"/>
-      <c r="J118" s="13" t="n"/>
-      <c r="K118" s="13" t="n"/>
+      <c r="J118" s="11" t="n"/>
       <c r="L118" s="13" t="n"/>
+      <c r="M118" s="13" t="n"/>
+      <c r="N118" s="13" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="11" t="n"/>
@@ -2987,7 +3055,8 @@
       <c r="G119" s="11" t="n"/>
       <c r="H119" s="11" t="n"/>
       <c r="I119" s="11" t="n"/>
-      <c r="J119" s="12" t="inlineStr">
+      <c r="J119" s="11" t="n"/>
+      <c r="L119" s="12" t="inlineStr">
         <is>
           <t>Set #8</t>
         </is>
@@ -3003,9 +3072,10 @@
       <c r="G120" s="11" t="n"/>
       <c r="H120" s="11" t="n"/>
       <c r="I120" s="11" t="n"/>
-      <c r="J120" s="13" t="n"/>
-      <c r="K120" s="13" t="n"/>
+      <c r="J120" s="11" t="n"/>
       <c r="L120" s="13" t="n"/>
+      <c r="M120" s="13" t="n"/>
+      <c r="N120" s="13" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="11" t="n"/>
@@ -3017,9 +3087,10 @@
       <c r="G121" s="11" t="n"/>
       <c r="H121" s="11" t="n"/>
       <c r="I121" s="11" t="n"/>
-      <c r="J121" s="13" t="n"/>
-      <c r="K121" s="13" t="n"/>
+      <c r="J121" s="11" t="n"/>
       <c r="L121" s="13" t="n"/>
+      <c r="M121" s="13" t="n"/>
+      <c r="N121" s="13" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="11" t="n"/>
@@ -3031,9 +3102,10 @@
       <c r="G122" s="11" t="n"/>
       <c r="H122" s="11" t="n"/>
       <c r="I122" s="11" t="n"/>
-      <c r="J122" s="13" t="n"/>
-      <c r="K122" s="13" t="n"/>
+      <c r="J122" s="11" t="n"/>
       <c r="L122" s="13" t="n"/>
+      <c r="M122" s="13" t="n"/>
+      <c r="N122" s="13" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="11" t="n"/>
@@ -3045,6 +3117,7 @@
       <c r="G123" s="11" t="n"/>
       <c r="H123" s="11" t="n"/>
       <c r="I123" s="11" t="n"/>
+      <c r="J123" s="11" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="11" t="n"/>
@@ -3056,7 +3129,8 @@
       <c r="G124" s="11" t="n"/>
       <c r="H124" s="11" t="n"/>
       <c r="I124" s="11" t="n"/>
-      <c r="J124" s="2" t="inlineStr">
+      <c r="J124" s="11" t="n"/>
+      <c r="L124" s="2" t="inlineStr">
         <is>
           <t>Album #3</t>
         </is>
@@ -3072,7 +3146,8 @@
       <c r="G125" s="11" t="n"/>
       <c r="H125" s="11" t="n"/>
       <c r="I125" s="11" t="n"/>
-      <c r="J125" s="12" t="inlineStr">
+      <c r="J125" s="11" t="n"/>
+      <c r="L125" s="12" t="inlineStr">
         <is>
           <t>Set #1</t>
         </is>
@@ -3088,9 +3163,10 @@
       <c r="G126" s="11" t="n"/>
       <c r="H126" s="11" t="n"/>
       <c r="I126" s="11" t="n"/>
-      <c r="J126" s="13" t="n"/>
-      <c r="K126" s="13" t="n"/>
+      <c r="J126" s="11" t="n"/>
       <c r="L126" s="13" t="n"/>
+      <c r="M126" s="13" t="n"/>
+      <c r="N126" s="13" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="11" t="n"/>
@@ -3102,9 +3178,10 @@
       <c r="G127" s="11" t="n"/>
       <c r="H127" s="11" t="n"/>
       <c r="I127" s="11" t="n"/>
-      <c r="J127" s="13" t="n"/>
-      <c r="K127" s="13" t="n"/>
+      <c r="J127" s="11" t="n"/>
       <c r="L127" s="13" t="n"/>
+      <c r="M127" s="13" t="n"/>
+      <c r="N127" s="13" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="11" t="n"/>
@@ -3116,9 +3193,10 @@
       <c r="G128" s="11" t="n"/>
       <c r="H128" s="11" t="n"/>
       <c r="I128" s="11" t="n"/>
-      <c r="J128" s="13" t="n"/>
-      <c r="K128" s="13" t="n"/>
+      <c r="J128" s="11" t="n"/>
       <c r="L128" s="13" t="n"/>
+      <c r="M128" s="13" t="n"/>
+      <c r="N128" s="13" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="11" t="n"/>
@@ -3130,7 +3208,8 @@
       <c r="G129" s="11" t="n"/>
       <c r="H129" s="11" t="n"/>
       <c r="I129" s="11" t="n"/>
-      <c r="J129" s="12" t="inlineStr">
+      <c r="J129" s="11" t="n"/>
+      <c r="L129" s="12" t="inlineStr">
         <is>
           <t>Set #2</t>
         </is>
@@ -3146,9 +3225,10 @@
       <c r="G130" s="11" t="n"/>
       <c r="H130" s="11" t="n"/>
       <c r="I130" s="11" t="n"/>
-      <c r="J130" s="13" t="n"/>
-      <c r="K130" s="13" t="n"/>
+      <c r="J130" s="11" t="n"/>
       <c r="L130" s="13" t="n"/>
+      <c r="M130" s="13" t="n"/>
+      <c r="N130" s="13" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="11" t="n"/>
@@ -3160,9 +3240,10 @@
       <c r="G131" s="11" t="n"/>
       <c r="H131" s="11" t="n"/>
       <c r="I131" s="11" t="n"/>
-      <c r="J131" s="13" t="n"/>
-      <c r="K131" s="13" t="n"/>
+      <c r="J131" s="11" t="n"/>
       <c r="L131" s="13" t="n"/>
+      <c r="M131" s="13" t="n"/>
+      <c r="N131" s="13" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="11" t="n"/>
@@ -3174,9 +3255,10 @@
       <c r="G132" s="11" t="n"/>
       <c r="H132" s="11" t="n"/>
       <c r="I132" s="11" t="n"/>
-      <c r="J132" s="13" t="n"/>
-      <c r="K132" s="13" t="n"/>
+      <c r="J132" s="11" t="n"/>
       <c r="L132" s="13" t="n"/>
+      <c r="M132" s="13" t="n"/>
+      <c r="N132" s="13" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="11" t="n"/>
@@ -3188,7 +3270,8 @@
       <c r="G133" s="11" t="n"/>
       <c r="H133" s="11" t="n"/>
       <c r="I133" s="11" t="n"/>
-      <c r="J133" s="12" t="inlineStr">
+      <c r="J133" s="11" t="n"/>
+      <c r="L133" s="12" t="inlineStr">
         <is>
           <t>Set #3</t>
         </is>
@@ -3204,9 +3287,10 @@
       <c r="G134" s="11" t="n"/>
       <c r="H134" s="11" t="n"/>
       <c r="I134" s="11" t="n"/>
-      <c r="J134" s="13" t="n"/>
-      <c r="K134" s="13" t="n"/>
+      <c r="J134" s="11" t="n"/>
       <c r="L134" s="13" t="n"/>
+      <c r="M134" s="13" t="n"/>
+      <c r="N134" s="13" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="11" t="n"/>
@@ -3218,9 +3302,10 @@
       <c r="G135" s="11" t="n"/>
       <c r="H135" s="11" t="n"/>
       <c r="I135" s="11" t="n"/>
-      <c r="J135" s="13" t="n"/>
-      <c r="K135" s="13" t="n"/>
+      <c r="J135" s="11" t="n"/>
       <c r="L135" s="13" t="n"/>
+      <c r="M135" s="13" t="n"/>
+      <c r="N135" s="13" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="11" t="n"/>
@@ -3232,9 +3317,10 @@
       <c r="G136" s="11" t="n"/>
       <c r="H136" s="11" t="n"/>
       <c r="I136" s="11" t="n"/>
-      <c r="J136" s="13" t="n"/>
-      <c r="K136" s="13" t="n"/>
+      <c r="J136" s="11" t="n"/>
       <c r="L136" s="13" t="n"/>
+      <c r="M136" s="13" t="n"/>
+      <c r="N136" s="13" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="11" t="n"/>
@@ -3246,7 +3332,8 @@
       <c r="G137" s="11" t="n"/>
       <c r="H137" s="11" t="n"/>
       <c r="I137" s="11" t="n"/>
-      <c r="J137" s="12" t="inlineStr">
+      <c r="J137" s="11" t="n"/>
+      <c r="L137" s="12" t="inlineStr">
         <is>
           <t>Set #4</t>
         </is>
@@ -3262,9 +3349,10 @@
       <c r="G138" s="11" t="n"/>
       <c r="H138" s="11" t="n"/>
       <c r="I138" s="11" t="n"/>
-      <c r="J138" s="13" t="n"/>
-      <c r="K138" s="13" t="n"/>
+      <c r="J138" s="11" t="n"/>
       <c r="L138" s="13" t="n"/>
+      <c r="M138" s="13" t="n"/>
+      <c r="N138" s="13" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="11" t="n"/>
@@ -3276,9 +3364,10 @@
       <c r="G139" s="11" t="n"/>
       <c r="H139" s="11" t="n"/>
       <c r="I139" s="11" t="n"/>
-      <c r="J139" s="13" t="n"/>
-      <c r="K139" s="13" t="n"/>
+      <c r="J139" s="11" t="n"/>
       <c r="L139" s="13" t="n"/>
+      <c r="M139" s="13" t="n"/>
+      <c r="N139" s="13" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="11" t="n"/>
@@ -3290,9 +3379,10 @@
       <c r="G140" s="11" t="n"/>
       <c r="H140" s="11" t="n"/>
       <c r="I140" s="11" t="n"/>
-      <c r="J140" s="13" t="n"/>
-      <c r="K140" s="13" t="n"/>
+      <c r="J140" s="11" t="n"/>
       <c r="L140" s="13" t="n"/>
+      <c r="M140" s="13" t="n"/>
+      <c r="N140" s="13" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="11" t="n"/>
@@ -3304,7 +3394,8 @@
       <c r="G141" s="11" t="n"/>
       <c r="H141" s="11" t="n"/>
       <c r="I141" s="11" t="n"/>
-      <c r="J141" s="12" t="inlineStr">
+      <c r="J141" s="11" t="n"/>
+      <c r="L141" s="12" t="inlineStr">
         <is>
           <t>Set #5</t>
         </is>
@@ -3320,9 +3411,10 @@
       <c r="G142" s="11" t="n"/>
       <c r="H142" s="11" t="n"/>
       <c r="I142" s="11" t="n"/>
-      <c r="J142" s="13" t="n"/>
-      <c r="K142" s="13" t="n"/>
+      <c r="J142" s="11" t="n"/>
       <c r="L142" s="13" t="n"/>
+      <c r="M142" s="13" t="n"/>
+      <c r="N142" s="13" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="11" t="n"/>
@@ -3334,9 +3426,10 @@
       <c r="G143" s="11" t="n"/>
       <c r="H143" s="11" t="n"/>
       <c r="I143" s="11" t="n"/>
-      <c r="J143" s="13" t="n"/>
-      <c r="K143" s="13" t="n"/>
+      <c r="J143" s="11" t="n"/>
       <c r="L143" s="13" t="n"/>
+      <c r="M143" s="13" t="n"/>
+      <c r="N143" s="13" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="11" t="n"/>
@@ -3348,9 +3441,10 @@
       <c r="G144" s="11" t="n"/>
       <c r="H144" s="11" t="n"/>
       <c r="I144" s="11" t="n"/>
-      <c r="J144" s="13" t="n"/>
-      <c r="K144" s="13" t="n"/>
+      <c r="J144" s="11" t="n"/>
       <c r="L144" s="13" t="n"/>
+      <c r="M144" s="13" t="n"/>
+      <c r="N144" s="13" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="11" t="n"/>
@@ -3362,7 +3456,8 @@
       <c r="G145" s="11" t="n"/>
       <c r="H145" s="11" t="n"/>
       <c r="I145" s="11" t="n"/>
-      <c r="J145" s="12" t="inlineStr">
+      <c r="J145" s="11" t="n"/>
+      <c r="L145" s="12" t="inlineStr">
         <is>
           <t>Set #6</t>
         </is>
@@ -3378,9 +3473,10 @@
       <c r="G146" s="11" t="n"/>
       <c r="H146" s="11" t="n"/>
       <c r="I146" s="11" t="n"/>
-      <c r="J146" s="13" t="n"/>
-      <c r="K146" s="13" t="n"/>
+      <c r="J146" s="11" t="n"/>
       <c r="L146" s="13" t="n"/>
+      <c r="M146" s="13" t="n"/>
+      <c r="N146" s="13" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="11" t="n"/>
@@ -3392,9 +3488,10 @@
       <c r="G147" s="11" t="n"/>
       <c r="H147" s="11" t="n"/>
       <c r="I147" s="11" t="n"/>
-      <c r="J147" s="13" t="n"/>
-      <c r="K147" s="13" t="n"/>
+      <c r="J147" s="11" t="n"/>
       <c r="L147" s="13" t="n"/>
+      <c r="M147" s="13" t="n"/>
+      <c r="N147" s="13" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="11" t="n"/>
@@ -3406,9 +3503,10 @@
       <c r="G148" s="11" t="n"/>
       <c r="H148" s="11" t="n"/>
       <c r="I148" s="11" t="n"/>
-      <c r="J148" s="13" t="n"/>
-      <c r="K148" s="13" t="n"/>
+      <c r="J148" s="11" t="n"/>
       <c r="L148" s="13" t="n"/>
+      <c r="M148" s="13" t="n"/>
+      <c r="N148" s="13" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="11" t="n"/>
@@ -3420,7 +3518,8 @@
       <c r="G149" s="11" t="n"/>
       <c r="H149" s="11" t="n"/>
       <c r="I149" s="11" t="n"/>
-      <c r="J149" s="12" t="inlineStr">
+      <c r="J149" s="11" t="n"/>
+      <c r="L149" s="12" t="inlineStr">
         <is>
           <t>Set #7</t>
         </is>
@@ -3436,9 +3535,10 @@
       <c r="G150" s="11" t="n"/>
       <c r="H150" s="11" t="n"/>
       <c r="I150" s="11" t="n"/>
-      <c r="J150" s="13" t="n"/>
-      <c r="K150" s="13" t="n"/>
+      <c r="J150" s="11" t="n"/>
       <c r="L150" s="13" t="n"/>
+      <c r="M150" s="13" t="n"/>
+      <c r="N150" s="13" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="11" t="n"/>
@@ -3450,9 +3550,10 @@
       <c r="G151" s="11" t="n"/>
       <c r="H151" s="11" t="n"/>
       <c r="I151" s="11" t="n"/>
-      <c r="J151" s="13" t="n"/>
-      <c r="K151" s="13" t="n"/>
+      <c r="J151" s="11" t="n"/>
       <c r="L151" s="13" t="n"/>
+      <c r="M151" s="13" t="n"/>
+      <c r="N151" s="13" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="11" t="n"/>
@@ -3464,9 +3565,10 @@
       <c r="G152" s="11" t="n"/>
       <c r="H152" s="11" t="n"/>
       <c r="I152" s="11" t="n"/>
-      <c r="J152" s="13" t="n"/>
-      <c r="K152" s="13" t="n"/>
+      <c r="J152" s="11" t="n"/>
       <c r="L152" s="13" t="n"/>
+      <c r="M152" s="13" t="n"/>
+      <c r="N152" s="13" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="11" t="n"/>
@@ -3478,7 +3580,8 @@
       <c r="G153" s="11" t="n"/>
       <c r="H153" s="11" t="n"/>
       <c r="I153" s="11" t="n"/>
-      <c r="J153" s="12" t="inlineStr">
+      <c r="J153" s="11" t="n"/>
+      <c r="L153" s="12" t="inlineStr">
         <is>
           <t>Set #8</t>
         </is>
@@ -3494,9 +3597,10 @@
       <c r="G154" s="11" t="n"/>
       <c r="H154" s="11" t="n"/>
       <c r="I154" s="11" t="n"/>
-      <c r="J154" s="13" t="n"/>
-      <c r="K154" s="13" t="n"/>
+      <c r="J154" s="11" t="n"/>
       <c r="L154" s="13" t="n"/>
+      <c r="M154" s="13" t="n"/>
+      <c r="N154" s="13" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="11" t="n"/>
@@ -3508,9 +3612,10 @@
       <c r="G155" s="11" t="n"/>
       <c r="H155" s="11" t="n"/>
       <c r="I155" s="11" t="n"/>
-      <c r="J155" s="13" t="n"/>
-      <c r="K155" s="13" t="n"/>
+      <c r="J155" s="11" t="n"/>
       <c r="L155" s="13" t="n"/>
+      <c r="M155" s="13" t="n"/>
+      <c r="N155" s="13" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="11" t="n"/>
@@ -3522,9 +3627,10 @@
       <c r="G156" s="11" t="n"/>
       <c r="H156" s="11" t="n"/>
       <c r="I156" s="11" t="n"/>
-      <c r="J156" s="13" t="n"/>
-      <c r="K156" s="13" t="n"/>
+      <c r="J156" s="11" t="n"/>
       <c r="L156" s="13" t="n"/>
+      <c r="M156" s="13" t="n"/>
+      <c r="N156" s="13" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="11" t="n"/>
@@ -3536,6 +3642,7 @@
       <c r="G157" s="11" t="n"/>
       <c r="H157" s="11" t="n"/>
       <c r="I157" s="11" t="n"/>
+      <c r="J157" s="11" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="11" t="n"/>
@@ -3547,6 +3654,7 @@
       <c r="G158" s="11" t="n"/>
       <c r="H158" s="11" t="n"/>
       <c r="I158" s="11" t="n"/>
+      <c r="J158" s="11" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="14" t="inlineStr">
@@ -3562,6 +3670,7 @@
       <c r="G159" s="11" t="n"/>
       <c r="H159" s="11" t="n"/>
       <c r="I159" s="11" t="n"/>
+      <c r="J159" s="11" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
@@ -3577,6 +3686,7 @@
       <c r="G160" s="11" t="n"/>
       <c r="H160" s="11" t="n"/>
       <c r="I160" s="11" t="n"/>
+      <c r="J160" s="11" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
@@ -3592,6 +3702,7 @@
       <c r="G161" s="11" t="n"/>
       <c r="H161" s="11" t="n"/>
       <c r="I161" s="11" t="n"/>
+      <c r="J161" s="11" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
@@ -3607,6 +3718,7 @@
       <c r="G162" s="11" t="n"/>
       <c r="H162" s="11" t="n"/>
       <c r="I162" s="11" t="n"/>
+      <c r="J162" s="11" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
@@ -3622,6 +3734,7 @@
       <c r="G163" s="11" t="n"/>
       <c r="H163" s="11" t="n"/>
       <c r="I163" s="11" t="n"/>
+      <c r="J163" s="11" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="11" t="n"/>
@@ -3633,6 +3746,7 @@
       <c r="G164" s="11" t="n"/>
       <c r="H164" s="11" t="n"/>
       <c r="I164" s="11" t="n"/>
+      <c r="J164" s="11" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="11" t="n"/>
@@ -3644,6 +3758,7 @@
       <c r="G165" s="11" t="n"/>
       <c r="H165" s="11" t="n"/>
       <c r="I165" s="11" t="n"/>
+      <c r="J165" s="11" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="11" t="n"/>
@@ -3655,6 +3770,7 @@
       <c r="G166" s="11" t="n"/>
       <c r="H166" s="11" t="n"/>
       <c r="I166" s="11" t="n"/>
+      <c r="J166" s="11" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="11" t="n"/>
@@ -3666,6 +3782,7 @@
       <c r="G167" s="11" t="n"/>
       <c r="H167" s="11" t="n"/>
       <c r="I167" s="11" t="n"/>
+      <c r="J167" s="11" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="11" t="n"/>
@@ -3677,6 +3794,7 @@
       <c r="G168" s="11" t="n"/>
       <c r="H168" s="11" t="n"/>
       <c r="I168" s="11" t="n"/>
+      <c r="J168" s="11" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="11" t="n"/>
@@ -3688,6 +3806,7 @@
       <c r="G169" s="11" t="n"/>
       <c r="H169" s="11" t="n"/>
       <c r="I169" s="11" t="n"/>
+      <c r="J169" s="11" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="11" t="n"/>
@@ -3699,6 +3818,7 @@
       <c r="G170" s="11" t="n"/>
       <c r="H170" s="11" t="n"/>
       <c r="I170" s="11" t="n"/>
+      <c r="J170" s="11" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="11" t="n"/>
@@ -3710,6 +3830,7 @@
       <c r="G171" s="11" t="n"/>
       <c r="H171" s="11" t="n"/>
       <c r="I171" s="11" t="n"/>
+      <c r="J171" s="11" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="11" t="n"/>
@@ -3721,6 +3842,7 @@
       <c r="G172" s="11" t="n"/>
       <c r="H172" s="11" t="n"/>
       <c r="I172" s="11" t="n"/>
+      <c r="J172" s="11" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="11" t="n"/>
@@ -3732,6 +3854,7 @@
       <c r="G173" s="11" t="n"/>
       <c r="H173" s="11" t="n"/>
       <c r="I173" s="11" t="n"/>
+      <c r="J173" s="11" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="11" t="n"/>
@@ -3743,6 +3866,7 @@
       <c r="G174" s="11" t="n"/>
       <c r="H174" s="11" t="n"/>
       <c r="I174" s="11" t="n"/>
+      <c r="J174" s="11" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="11" t="n"/>
@@ -3754,6 +3878,7 @@
       <c r="G175" s="11" t="n"/>
       <c r="H175" s="11" t="n"/>
       <c r="I175" s="11" t="n"/>
+      <c r="J175" s="11" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="11" t="n"/>
@@ -3765,6 +3890,7 @@
       <c r="G176" s="11" t="n"/>
       <c r="H176" s="11" t="n"/>
       <c r="I176" s="11" t="n"/>
+      <c r="J176" s="11" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="11" t="n"/>
@@ -3776,6 +3902,7 @@
       <c r="G177" s="11" t="n"/>
       <c r="H177" s="11" t="n"/>
       <c r="I177" s="11" t="n"/>
+      <c r="J177" s="11" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="11" t="n"/>
@@ -3787,6 +3914,7 @@
       <c r="G178" s="11" t="n"/>
       <c r="H178" s="11" t="n"/>
       <c r="I178" s="11" t="n"/>
+      <c r="J178" s="11" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="11" t="n"/>
@@ -3798,6 +3926,7 @@
       <c r="G179" s="11" t="n"/>
       <c r="H179" s="11" t="n"/>
       <c r="I179" s="11" t="n"/>
+      <c r="J179" s="11" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="11" t="n"/>
@@ -3809,6 +3938,7 @@
       <c r="G180" s="11" t="n"/>
       <c r="H180" s="11" t="n"/>
       <c r="I180" s="11" t="n"/>
+      <c r="J180" s="11" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="11" t="n"/>
@@ -3820,6 +3950,7 @@
       <c r="G181" s="11" t="n"/>
       <c r="H181" s="11" t="n"/>
       <c r="I181" s="11" t="n"/>
+      <c r="J181" s="11" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="11" t="n"/>
@@ -3831,6 +3962,7 @@
       <c r="G182" s="11" t="n"/>
       <c r="H182" s="11" t="n"/>
       <c r="I182" s="11" t="n"/>
+      <c r="J182" s="11" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="11" t="n"/>
@@ -3842,6 +3974,7 @@
       <c r="G183" s="11" t="n"/>
       <c r="H183" s="11" t="n"/>
       <c r="I183" s="11" t="n"/>
+      <c r="J183" s="11" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="11" t="n"/>
@@ -3853,6 +3986,7 @@
       <c r="G184" s="11" t="n"/>
       <c r="H184" s="11" t="n"/>
       <c r="I184" s="11" t="n"/>
+      <c r="J184" s="11" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="11" t="n"/>
@@ -3864,6 +3998,7 @@
       <c r="G185" s="11" t="n"/>
       <c r="H185" s="11" t="n"/>
       <c r="I185" s="11" t="n"/>
+      <c r="J185" s="11" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="11" t="n"/>
@@ -3875,6 +4010,7 @@
       <c r="G186" s="11" t="n"/>
       <c r="H186" s="11" t="n"/>
       <c r="I186" s="11" t="n"/>
+      <c r="J186" s="11" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="11" t="n"/>
@@ -3886,6 +4022,7 @@
       <c r="G187" s="11" t="n"/>
       <c r="H187" s="11" t="n"/>
       <c r="I187" s="11" t="n"/>
+      <c r="J187" s="11" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="11" t="n"/>
@@ -3897,6 +4034,7 @@
       <c r="G188" s="11" t="n"/>
       <c r="H188" s="11" t="n"/>
       <c r="I188" s="11" t="n"/>
+      <c r="J188" s="11" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="11" t="n"/>
@@ -3908,6 +4046,7 @@
       <c r="G189" s="11" t="n"/>
       <c r="H189" s="11" t="n"/>
       <c r="I189" s="11" t="n"/>
+      <c r="J189" s="11" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="11" t="n"/>
@@ -3919,6 +4058,7 @@
       <c r="G190" s="11" t="n"/>
       <c r="H190" s="11" t="n"/>
       <c r="I190" s="11" t="n"/>
+      <c r="J190" s="11" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="11" t="n"/>
@@ -3930,6 +4070,7 @@
       <c r="G191" s="11" t="n"/>
       <c r="H191" s="11" t="n"/>
       <c r="I191" s="11" t="n"/>
+      <c r="J191" s="11" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="11" t="n"/>
@@ -3941,6 +4082,7 @@
       <c r="G192" s="11" t="n"/>
       <c r="H192" s="11" t="n"/>
       <c r="I192" s="11" t="n"/>
+      <c r="J192" s="11" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="11" t="n"/>
@@ -3952,6 +4094,7 @@
       <c r="G193" s="11" t="n"/>
       <c r="H193" s="11" t="n"/>
       <c r="I193" s="11" t="n"/>
+      <c r="J193" s="11" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="11" t="n"/>
@@ -3963,6 +4106,7 @@
       <c r="G194" s="11" t="n"/>
       <c r="H194" s="11" t="n"/>
       <c r="I194" s="11" t="n"/>
+      <c r="J194" s="11" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="11" t="n"/>
@@ -3974,6 +4118,7 @@
       <c r="G195" s="11" t="n"/>
       <c r="H195" s="11" t="n"/>
       <c r="I195" s="11" t="n"/>
+      <c r="J195" s="11" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="11" t="n"/>
@@ -3985,6 +4130,7 @@
       <c r="G196" s="11" t="n"/>
       <c r="H196" s="11" t="n"/>
       <c r="I196" s="11" t="n"/>
+      <c r="J196" s="11" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="11" t="n"/>
@@ -3996,6 +4142,7 @@
       <c r="G197" s="11" t="n"/>
       <c r="H197" s="11" t="n"/>
       <c r="I197" s="11" t="n"/>
+      <c r="J197" s="11" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="11" t="n"/>
@@ -4007,6 +4154,7 @@
       <c r="G198" s="11" t="n"/>
       <c r="H198" s="11" t="n"/>
       <c r="I198" s="11" t="n"/>
+      <c r="J198" s="11" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="11" t="n"/>
@@ -4018,6 +4166,7 @@
       <c r="G199" s="11" t="n"/>
       <c r="H199" s="11" t="n"/>
       <c r="I199" s="11" t="n"/>
+      <c r="J199" s="11" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="11" t="n"/>
@@ -4029,6 +4178,7 @@
       <c r="G200" s="11" t="n"/>
       <c r="H200" s="11" t="n"/>
       <c r="I200" s="11" t="n"/>
+      <c r="J200" s="11" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="11" t="n"/>
@@ -4040,6 +4190,7 @@
       <c r="G201" s="11" t="n"/>
       <c r="H201" s="11" t="n"/>
       <c r="I201" s="11" t="n"/>
+      <c r="J201" s="11" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="11" t="n"/>
@@ -4051,6 +4202,7 @@
       <c r="G202" s="11" t="n"/>
       <c r="H202" s="11" t="n"/>
       <c r="I202" s="11" t="n"/>
+      <c r="J202" s="11" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="11" t="n"/>
@@ -4062,6 +4214,7 @@
       <c r="G203" s="11" t="n"/>
       <c r="H203" s="11" t="n"/>
       <c r="I203" s="11" t="n"/>
+      <c r="J203" s="11" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="11" t="n"/>
@@ -4073,6 +4226,7 @@
       <c r="G204" s="11" t="n"/>
       <c r="H204" s="11" t="n"/>
       <c r="I204" s="11" t="n"/>
+      <c r="J204" s="11" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="11" t="n"/>
@@ -4084,6 +4238,7 @@
       <c r="G205" s="11" t="n"/>
       <c r="H205" s="11" t="n"/>
       <c r="I205" s="11" t="n"/>
+      <c r="J205" s="11" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="11" t="n"/>
@@ -4095,6 +4250,7 @@
       <c r="G206" s="11" t="n"/>
       <c r="H206" s="11" t="n"/>
       <c r="I206" s="11" t="n"/>
+      <c r="J206" s="11" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="11" t="n"/>
@@ -4106,6 +4262,7 @@
       <c r="G207" s="11" t="n"/>
       <c r="H207" s="11" t="n"/>
       <c r="I207" s="11" t="n"/>
+      <c r="J207" s="11" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="11" t="n"/>
@@ -4117,6 +4274,7 @@
       <c r="G208" s="11" t="n"/>
       <c r="H208" s="11" t="n"/>
       <c r="I208" s="11" t="n"/>
+      <c r="J208" s="11" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="11" t="n"/>
@@ -4128,6 +4286,7 @@
       <c r="G209" s="11" t="n"/>
       <c r="H209" s="11" t="n"/>
       <c r="I209" s="11" t="n"/>
+      <c r="J209" s="11" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="11" t="n"/>
@@ -4139,6 +4298,7 @@
       <c r="G210" s="11" t="n"/>
       <c r="H210" s="11" t="n"/>
       <c r="I210" s="11" t="n"/>
+      <c r="J210" s="11" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="11" t="n"/>
@@ -4150,6 +4310,7 @@
       <c r="G211" s="11" t="n"/>
       <c r="H211" s="11" t="n"/>
       <c r="I211" s="11" t="n"/>
+      <c r="J211" s="11" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="11" t="n"/>
@@ -4161,6 +4322,7 @@
       <c r="G212" s="11" t="n"/>
       <c r="H212" s="11" t="n"/>
       <c r="I212" s="11" t="n"/>
+      <c r="J212" s="11" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="11" t="n"/>
@@ -4172,6 +4334,7 @@
       <c r="G213" s="11" t="n"/>
       <c r="H213" s="11" t="n"/>
       <c r="I213" s="11" t="n"/>
+      <c r="J213" s="11" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="11" t="n"/>
@@ -4183,6 +4346,7 @@
       <c r="G214" s="11" t="n"/>
       <c r="H214" s="11" t="n"/>
       <c r="I214" s="11" t="n"/>
+      <c r="J214" s="11" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="11" t="n"/>
@@ -4194,6 +4358,7 @@
       <c r="G215" s="11" t="n"/>
       <c r="H215" s="11" t="n"/>
       <c r="I215" s="11" t="n"/>
+      <c r="J215" s="11" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="11" t="n"/>
@@ -4205,6 +4370,7 @@
       <c r="G216" s="11" t="n"/>
       <c r="H216" s="11" t="n"/>
       <c r="I216" s="11" t="n"/>
+      <c r="J216" s="11" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="11" t="n"/>
@@ -4216,6 +4382,7 @@
       <c r="G217" s="11" t="n"/>
       <c r="H217" s="11" t="n"/>
       <c r="I217" s="11" t="n"/>
+      <c r="J217" s="11" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="11" t="n"/>
@@ -4227,6 +4394,7 @@
       <c r="G218" s="11" t="n"/>
       <c r="H218" s="11" t="n"/>
       <c r="I218" s="11" t="n"/>
+      <c r="J218" s="11" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="11" t="n"/>
@@ -4238,6 +4406,7 @@
       <c r="G219" s="11" t="n"/>
       <c r="H219" s="11" t="n"/>
       <c r="I219" s="11" t="n"/>
+      <c r="J219" s="11" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="11" t="n"/>
@@ -4249,6 +4418,7 @@
       <c r="G220" s="11" t="n"/>
       <c r="H220" s="11" t="n"/>
       <c r="I220" s="11" t="n"/>
+      <c r="J220" s="11" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="11" t="n"/>
@@ -4260,6 +4430,7 @@
       <c r="G221" s="11" t="n"/>
       <c r="H221" s="11" t="n"/>
       <c r="I221" s="11" t="n"/>
+      <c r="J221" s="11" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="11" t="n"/>
@@ -4271,6 +4442,7 @@
       <c r="G222" s="11" t="n"/>
       <c r="H222" s="11" t="n"/>
       <c r="I222" s="11" t="n"/>
+      <c r="J222" s="11" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="11" t="n"/>
@@ -4282,6 +4454,7 @@
       <c r="G223" s="11" t="n"/>
       <c r="H223" s="11" t="n"/>
       <c r="I223" s="11" t="n"/>
+      <c r="J223" s="11" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="11" t="n"/>
@@ -4293,6 +4466,7 @@
       <c r="G224" s="11" t="n"/>
       <c r="H224" s="11" t="n"/>
       <c r="I224" s="11" t="n"/>
+      <c r="J224" s="11" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="11" t="n"/>
@@ -4304,6 +4478,7 @@
       <c r="G225" s="11" t="n"/>
       <c r="H225" s="11" t="n"/>
       <c r="I225" s="11" t="n"/>
+      <c r="J225" s="11" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="11" t="n"/>
@@ -4315,6 +4490,7 @@
       <c r="G226" s="11" t="n"/>
       <c r="H226" s="11" t="n"/>
       <c r="I226" s="11" t="n"/>
+      <c r="J226" s="11" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="11" t="n"/>
@@ -4326,6 +4502,7 @@
       <c r="G227" s="11" t="n"/>
       <c r="H227" s="11" t="n"/>
       <c r="I227" s="11" t="n"/>
+      <c r="J227" s="11" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="11" t="n"/>
@@ -4337,6 +4514,7 @@
       <c r="G228" s="11" t="n"/>
       <c r="H228" s="11" t="n"/>
       <c r="I228" s="11" t="n"/>
+      <c r="J228" s="11" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="11" t="n"/>
@@ -4348,6 +4526,7 @@
       <c r="G229" s="11" t="n"/>
       <c r="H229" s="11" t="n"/>
       <c r="I229" s="11" t="n"/>
+      <c r="J229" s="11" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="11" t="n"/>
@@ -4359,6 +4538,7 @@
       <c r="G230" s="11" t="n"/>
       <c r="H230" s="11" t="n"/>
       <c r="I230" s="11" t="n"/>
+      <c r="J230" s="11" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="11" t="n"/>
@@ -4370,6 +4550,7 @@
       <c r="G231" s="11" t="n"/>
       <c r="H231" s="11" t="n"/>
       <c r="I231" s="11" t="n"/>
+      <c r="J231" s="11" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="11" t="n"/>
@@ -4381,6 +4562,7 @@
       <c r="G232" s="11" t="n"/>
       <c r="H232" s="11" t="n"/>
       <c r="I232" s="11" t="n"/>
+      <c r="J232" s="11" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="11" t="n"/>
@@ -4392,6 +4574,7 @@
       <c r="G233" s="11" t="n"/>
       <c r="H233" s="11" t="n"/>
       <c r="I233" s="11" t="n"/>
+      <c r="J233" s="11" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="11" t="n"/>
@@ -4403,6 +4586,7 @@
       <c r="G234" s="11" t="n"/>
       <c r="H234" s="11" t="n"/>
       <c r="I234" s="11" t="n"/>
+      <c r="J234" s="11" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="11" t="n"/>
@@ -4414,6 +4598,7 @@
       <c r="G235" s="11" t="n"/>
       <c r="H235" s="11" t="n"/>
       <c r="I235" s="11" t="n"/>
+      <c r="J235" s="11" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="11" t="n"/>
@@ -4425,6 +4610,7 @@
       <c r="G236" s="11" t="n"/>
       <c r="H236" s="11" t="n"/>
       <c r="I236" s="11" t="n"/>
+      <c r="J236" s="11" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="11" t="n"/>
@@ -4436,6 +4622,7 @@
       <c r="G237" s="11" t="n"/>
       <c r="H237" s="11" t="n"/>
       <c r="I237" s="11" t="n"/>
+      <c r="J237" s="11" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="11" t="n"/>
@@ -4447,6 +4634,7 @@
       <c r="G238" s="11" t="n"/>
       <c r="H238" s="11" t="n"/>
       <c r="I238" s="11" t="n"/>
+      <c r="J238" s="11" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="11" t="n"/>
@@ -4458,6 +4646,7 @@
       <c r="G239" s="11" t="n"/>
       <c r="H239" s="11" t="n"/>
       <c r="I239" s="11" t="n"/>
+      <c r="J239" s="11" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="11" t="n"/>
@@ -4469,6 +4658,7 @@
       <c r="G240" s="11" t="n"/>
       <c r="H240" s="11" t="n"/>
       <c r="I240" s="11" t="n"/>
+      <c r="J240" s="11" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="11" t="n"/>
@@ -4480,6 +4670,7 @@
       <c r="G241" s="11" t="n"/>
       <c r="H241" s="11" t="n"/>
       <c r="I241" s="11" t="n"/>
+      <c r="J241" s="11" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="11" t="n"/>
@@ -4491,6 +4682,7 @@
       <c r="G242" s="11" t="n"/>
       <c r="H242" s="11" t="n"/>
       <c r="I242" s="11" t="n"/>
+      <c r="J242" s="11" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="11" t="n"/>
@@ -4502,6 +4694,7 @@
       <c r="G243" s="11" t="n"/>
       <c r="H243" s="11" t="n"/>
       <c r="I243" s="11" t="n"/>
+      <c r="J243" s="11" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="11" t="n"/>
@@ -4513,6 +4706,7 @@
       <c r="G244" s="11" t="n"/>
       <c r="H244" s="11" t="n"/>
       <c r="I244" s="11" t="n"/>
+      <c r="J244" s="11" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="11" t="n"/>
@@ -4524,6 +4718,7 @@
       <c r="G245" s="11" t="n"/>
       <c r="H245" s="11" t="n"/>
       <c r="I245" s="11" t="n"/>
+      <c r="J245" s="11" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="11" t="n"/>
@@ -4535,6 +4730,7 @@
       <c r="G246" s="11" t="n"/>
       <c r="H246" s="11" t="n"/>
       <c r="I246" s="11" t="n"/>
+      <c r="J246" s="11" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="11" t="n"/>
@@ -4546,6 +4742,7 @@
       <c r="G247" s="11" t="n"/>
       <c r="H247" s="11" t="n"/>
       <c r="I247" s="11" t="n"/>
+      <c r="J247" s="11" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="11" t="n"/>
@@ -4557,6 +4754,7 @@
       <c r="G248" s="11" t="n"/>
       <c r="H248" s="11" t="n"/>
       <c r="I248" s="11" t="n"/>
+      <c r="J248" s="11" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="11" t="n"/>
@@ -4568,6 +4766,7 @@
       <c r="G249" s="11" t="n"/>
       <c r="H249" s="11" t="n"/>
       <c r="I249" s="11" t="n"/>
+      <c r="J249" s="11" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="11" t="n"/>
@@ -4579,6 +4778,7 @@
       <c r="G250" s="11" t="n"/>
       <c r="H250" s="11" t="n"/>
       <c r="I250" s="11" t="n"/>
+      <c r="J250" s="11" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="11" t="n"/>
@@ -4590,6 +4790,7 @@
       <c r="G251" s="11" t="n"/>
       <c r="H251" s="11" t="n"/>
       <c r="I251" s="11" t="n"/>
+      <c r="J251" s="11" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="11" t="n"/>
@@ -4601,6 +4802,7 @@
       <c r="G252" s="11" t="n"/>
       <c r="H252" s="11" t="n"/>
       <c r="I252" s="11" t="n"/>
+      <c r="J252" s="11" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="11" t="n"/>
@@ -4612,6 +4814,7 @@
       <c r="G253" s="11" t="n"/>
       <c r="H253" s="11" t="n"/>
       <c r="I253" s="11" t="n"/>
+      <c r="J253" s="11" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="11" t="n"/>
@@ -4623,6 +4826,7 @@
       <c r="G254" s="11" t="n"/>
       <c r="H254" s="11" t="n"/>
       <c r="I254" s="11" t="n"/>
+      <c r="J254" s="11" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="11" t="n"/>
@@ -4634,6 +4838,7 @@
       <c r="G255" s="11" t="n"/>
       <c r="H255" s="11" t="n"/>
       <c r="I255" s="11" t="n"/>
+      <c r="J255" s="11" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="11" t="n"/>
@@ -4645,6 +4850,7 @@
       <c r="G256" s="11" t="n"/>
       <c r="H256" s="11" t="n"/>
       <c r="I256" s="11" t="n"/>
+      <c r="J256" s="11" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="11" t="n"/>
@@ -4656,6 +4862,7 @@
       <c r="G257" s="11" t="n"/>
       <c r="H257" s="11" t="n"/>
       <c r="I257" s="11" t="n"/>
+      <c r="J257" s="11" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="11" t="n"/>
@@ -4667,6 +4874,7 @@
       <c r="G258" s="11" t="n"/>
       <c r="H258" s="11" t="n"/>
       <c r="I258" s="11" t="n"/>
+      <c r="J258" s="11" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="11" t="n"/>
@@ -4678,6 +4886,7 @@
       <c r="G259" s="11" t="n"/>
       <c r="H259" s="11" t="n"/>
       <c r="I259" s="11" t="n"/>
+      <c r="J259" s="11" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="11" t="n"/>
@@ -4689,6 +4898,7 @@
       <c r="G260" s="11" t="n"/>
       <c r="H260" s="11" t="n"/>
       <c r="I260" s="11" t="n"/>
+      <c r="J260" s="11" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="11" t="n"/>
@@ -4700,6 +4910,7 @@
       <c r="G261" s="11" t="n"/>
       <c r="H261" s="11" t="n"/>
       <c r="I261" s="11" t="n"/>
+      <c r="J261" s="11" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="11" t="n"/>
@@ -4711,6 +4922,7 @@
       <c r="G262" s="11" t="n"/>
       <c r="H262" s="11" t="n"/>
       <c r="I262" s="11" t="n"/>
+      <c r="J262" s="11" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="11" t="n"/>
@@ -4722,6 +4934,7 @@
       <c r="G263" s="11" t="n"/>
       <c r="H263" s="11" t="n"/>
       <c r="I263" s="11" t="n"/>
+      <c r="J263" s="11" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="11" t="n"/>
@@ -4733,6 +4946,7 @@
       <c r="G264" s="11" t="n"/>
       <c r="H264" s="11" t="n"/>
       <c r="I264" s="11" t="n"/>
+      <c r="J264" s="11" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="11" t="n"/>
@@ -4744,6 +4958,7 @@
       <c r="G265" s="11" t="n"/>
       <c r="H265" s="11" t="n"/>
       <c r="I265" s="11" t="n"/>
+      <c r="J265" s="11" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="11" t="n"/>
@@ -4755,6 +4970,7 @@
       <c r="G266" s="11" t="n"/>
       <c r="H266" s="11" t="n"/>
       <c r="I266" s="11" t="n"/>
+      <c r="J266" s="11" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="11" t="n"/>
@@ -4766,6 +4982,7 @@
       <c r="G267" s="11" t="n"/>
       <c r="H267" s="11" t="n"/>
       <c r="I267" s="11" t="n"/>
+      <c r="J267" s="11" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="11" t="n"/>
@@ -4777,6 +4994,7 @@
       <c r="G268" s="11" t="n"/>
       <c r="H268" s="11" t="n"/>
       <c r="I268" s="11" t="n"/>
+      <c r="J268" s="11" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="11" t="n"/>
@@ -4788,6 +5006,7 @@
       <c r="G269" s="11" t="n"/>
       <c r="H269" s="11" t="n"/>
       <c r="I269" s="11" t="n"/>
+      <c r="J269" s="11" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="11" t="n"/>
@@ -4799,6 +5018,7 @@
       <c r="G270" s="11" t="n"/>
       <c r="H270" s="11" t="n"/>
       <c r="I270" s="11" t="n"/>
+      <c r="J270" s="11" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="11" t="n"/>
@@ -4810,6 +5030,7 @@
       <c r="G271" s="11" t="n"/>
       <c r="H271" s="11" t="n"/>
       <c r="I271" s="11" t="n"/>
+      <c r="J271" s="11" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="11" t="n"/>
@@ -4821,6 +5042,7 @@
       <c r="G272" s="11" t="n"/>
       <c r="H272" s="11" t="n"/>
       <c r="I272" s="11" t="n"/>
+      <c r="J272" s="11" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="11" t="n"/>
@@ -4832,6 +5054,7 @@
       <c r="G273" s="11" t="n"/>
       <c r="H273" s="11" t="n"/>
       <c r="I273" s="11" t="n"/>
+      <c r="J273" s="11" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="11" t="n"/>
@@ -4843,6 +5066,7 @@
       <c r="G274" s="11" t="n"/>
       <c r="H274" s="11" t="n"/>
       <c r="I274" s="11" t="n"/>
+      <c r="J274" s="11" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="11" t="n"/>
@@ -4854,6 +5078,7 @@
       <c r="G275" s="11" t="n"/>
       <c r="H275" s="11" t="n"/>
       <c r="I275" s="11" t="n"/>
+      <c r="J275" s="11" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="11" t="n"/>
@@ -4865,6 +5090,7 @@
       <c r="G276" s="11" t="n"/>
       <c r="H276" s="11" t="n"/>
       <c r="I276" s="11" t="n"/>
+      <c r="J276" s="11" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="2">

--- a/display/SimOutput_v2.xlsx
+++ b/display/SimOutput_v2.xlsx
@@ -2047,7 +2047,7 @@
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>Earned From</t>
+          <t>Source_Detail</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">

--- a/display/SimOutput_v2.xlsx
+++ b/display/SimOutput_v2.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O276"/>
+  <dimension ref="A1:P276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -518,10 +518,10 @@
     <col width="30" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="12" max="12"/>
     <col width="9" customWidth="1" min="13" max="13"/>
     <col width="9" customWidth="1" min="14" max="14"/>
     <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2045,14 +2045,15 @@
       <c r="H55" s="6" t="n"/>
       <c r="I55" s="6" t="n"/>
       <c r="J55" s="6" t="n"/>
-      <c r="L55" s="5" t="inlineStr">
+      <c r="K55" s="6" t="n"/>
+      <c r="M55" s="5" t="inlineStr">
         <is>
           <t>PACKS RESULT</t>
         </is>
       </c>
-      <c r="M55" s="6" t="n"/>
       <c r="N55" s="6" t="n"/>
       <c r="O55" s="6" t="n"/>
+      <c r="P55" s="6" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
@@ -2105,7 +2106,12 @@
           <t>Note</t>
         </is>
       </c>
-      <c r="L56" s="2" t="inlineStr">
+      <c r="K56" s="7" t="inlineStr">
+        <is>
+          <t>ToF Tickets (cum)</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
         <is>
           <t>Album #1</t>
         </is>
@@ -2122,7 +2128,8 @@
       <c r="H57" s="12" t="n"/>
       <c r="I57" s="12" t="n"/>
       <c r="J57" s="12" t="n"/>
-      <c r="L57" s="13" t="inlineStr">
+      <c r="K57" s="12" t="n"/>
+      <c r="M57" s="13" t="inlineStr">
         <is>
           <t>Set #1</t>
         </is>
@@ -2139,9 +2146,10 @@
       <c r="H58" s="12" t="n"/>
       <c r="I58" s="12" t="n"/>
       <c r="J58" s="12" t="n"/>
-      <c r="L58" s="14" t="n"/>
+      <c r="K58" s="12" t="n"/>
       <c r="M58" s="14" t="n"/>
       <c r="N58" s="14" t="n"/>
+      <c r="O58" s="14" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="12" t="n"/>
@@ -2154,9 +2162,10 @@
       <c r="H59" s="12" t="n"/>
       <c r="I59" s="12" t="n"/>
       <c r="J59" s="12" t="n"/>
-      <c r="L59" s="14" t="n"/>
+      <c r="K59" s="12" t="n"/>
       <c r="M59" s="14" t="n"/>
       <c r="N59" s="14" t="n"/>
+      <c r="O59" s="14" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="12" t="n"/>
@@ -2169,9 +2178,10 @@
       <c r="H60" s="12" t="n"/>
       <c r="I60" s="12" t="n"/>
       <c r="J60" s="12" t="n"/>
-      <c r="L60" s="14" t="n"/>
+      <c r="K60" s="12" t="n"/>
       <c r="M60" s="14" t="n"/>
       <c r="N60" s="14" t="n"/>
+      <c r="O60" s="14" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="12" t="n"/>
@@ -2184,7 +2194,8 @@
       <c r="H61" s="12" t="n"/>
       <c r="I61" s="12" t="n"/>
       <c r="J61" s="12" t="n"/>
-      <c r="L61" s="13" t="inlineStr">
+      <c r="K61" s="12" t="n"/>
+      <c r="M61" s="13" t="inlineStr">
         <is>
           <t>Set #2</t>
         </is>
@@ -2201,9 +2212,10 @@
       <c r="H62" s="12" t="n"/>
       <c r="I62" s="12" t="n"/>
       <c r="J62" s="12" t="n"/>
-      <c r="L62" s="14" t="n"/>
+      <c r="K62" s="12" t="n"/>
       <c r="M62" s="14" t="n"/>
       <c r="N62" s="14" t="n"/>
+      <c r="O62" s="14" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="12" t="n"/>
@@ -2216,9 +2228,10 @@
       <c r="H63" s="12" t="n"/>
       <c r="I63" s="12" t="n"/>
       <c r="J63" s="12" t="n"/>
-      <c r="L63" s="14" t="n"/>
+      <c r="K63" s="12" t="n"/>
       <c r="M63" s="14" t="n"/>
       <c r="N63" s="14" t="n"/>
+      <c r="O63" s="14" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="12" t="n"/>
@@ -2231,9 +2244,10 @@
       <c r="H64" s="12" t="n"/>
       <c r="I64" s="12" t="n"/>
       <c r="J64" s="12" t="n"/>
-      <c r="L64" s="14" t="n"/>
+      <c r="K64" s="12" t="n"/>
       <c r="M64" s="14" t="n"/>
       <c r="N64" s="14" t="n"/>
+      <c r="O64" s="14" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="12" t="n"/>
@@ -2246,7 +2260,8 @@
       <c r="H65" s="12" t="n"/>
       <c r="I65" s="12" t="n"/>
       <c r="J65" s="12" t="n"/>
-      <c r="L65" s="13" t="inlineStr">
+      <c r="K65" s="12" t="n"/>
+      <c r="M65" s="13" t="inlineStr">
         <is>
           <t>Set #3</t>
         </is>
@@ -2263,9 +2278,10 @@
       <c r="H66" s="12" t="n"/>
       <c r="I66" s="12" t="n"/>
       <c r="J66" s="12" t="n"/>
-      <c r="L66" s="14" t="n"/>
+      <c r="K66" s="12" t="n"/>
       <c r="M66" s="14" t="n"/>
       <c r="N66" s="14" t="n"/>
+      <c r="O66" s="14" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="12" t="n"/>
@@ -2278,9 +2294,10 @@
       <c r="H67" s="12" t="n"/>
       <c r="I67" s="12" t="n"/>
       <c r="J67" s="12" t="n"/>
-      <c r="L67" s="14" t="n"/>
+      <c r="K67" s="12" t="n"/>
       <c r="M67" s="14" t="n"/>
       <c r="N67" s="14" t="n"/>
+      <c r="O67" s="14" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="12" t="n"/>
@@ -2293,9 +2310,10 @@
       <c r="H68" s="12" t="n"/>
       <c r="I68" s="12" t="n"/>
       <c r="J68" s="12" t="n"/>
-      <c r="L68" s="14" t="n"/>
+      <c r="K68" s="12" t="n"/>
       <c r="M68" s="14" t="n"/>
       <c r="N68" s="14" t="n"/>
+      <c r="O68" s="14" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="12" t="n"/>
@@ -2308,7 +2326,8 @@
       <c r="H69" s="12" t="n"/>
       <c r="I69" s="12" t="n"/>
       <c r="J69" s="12" t="n"/>
-      <c r="L69" s="13" t="inlineStr">
+      <c r="K69" s="12" t="n"/>
+      <c r="M69" s="13" t="inlineStr">
         <is>
           <t>Set #4</t>
         </is>
@@ -2325,9 +2344,10 @@
       <c r="H70" s="12" t="n"/>
       <c r="I70" s="12" t="n"/>
       <c r="J70" s="12" t="n"/>
-      <c r="L70" s="14" t="n"/>
+      <c r="K70" s="12" t="n"/>
       <c r="M70" s="14" t="n"/>
       <c r="N70" s="14" t="n"/>
+      <c r="O70" s="14" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="12" t="n"/>
@@ -2340,9 +2360,10 @@
       <c r="H71" s="12" t="n"/>
       <c r="I71" s="12" t="n"/>
       <c r="J71" s="12" t="n"/>
-      <c r="L71" s="14" t="n"/>
+      <c r="K71" s="12" t="n"/>
       <c r="M71" s="14" t="n"/>
       <c r="N71" s="14" t="n"/>
+      <c r="O71" s="14" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="12" t="n"/>
@@ -2355,9 +2376,10 @@
       <c r="H72" s="12" t="n"/>
       <c r="I72" s="12" t="n"/>
       <c r="J72" s="12" t="n"/>
-      <c r="L72" s="14" t="n"/>
+      <c r="K72" s="12" t="n"/>
       <c r="M72" s="14" t="n"/>
       <c r="N72" s="14" t="n"/>
+      <c r="O72" s="14" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="12" t="n"/>
@@ -2370,7 +2392,8 @@
       <c r="H73" s="12" t="n"/>
       <c r="I73" s="12" t="n"/>
       <c r="J73" s="12" t="n"/>
-      <c r="L73" s="13" t="inlineStr">
+      <c r="K73" s="12" t="n"/>
+      <c r="M73" s="13" t="inlineStr">
         <is>
           <t>Set #5</t>
         </is>
@@ -2387,9 +2410,10 @@
       <c r="H74" s="12" t="n"/>
       <c r="I74" s="12" t="n"/>
       <c r="J74" s="12" t="n"/>
-      <c r="L74" s="14" t="n"/>
+      <c r="K74" s="12" t="n"/>
       <c r="M74" s="14" t="n"/>
       <c r="N74" s="14" t="n"/>
+      <c r="O74" s="14" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="12" t="n"/>
@@ -2402,9 +2426,10 @@
       <c r="H75" s="12" t="n"/>
       <c r="I75" s="12" t="n"/>
       <c r="J75" s="12" t="n"/>
-      <c r="L75" s="14" t="n"/>
+      <c r="K75" s="12" t="n"/>
       <c r="M75" s="14" t="n"/>
       <c r="N75" s="14" t="n"/>
+      <c r="O75" s="14" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="12" t="n"/>
@@ -2417,9 +2442,10 @@
       <c r="H76" s="12" t="n"/>
       <c r="I76" s="12" t="n"/>
       <c r="J76" s="12" t="n"/>
-      <c r="L76" s="14" t="n"/>
+      <c r="K76" s="12" t="n"/>
       <c r="M76" s="14" t="n"/>
       <c r="N76" s="14" t="n"/>
+      <c r="O76" s="14" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="12" t="n"/>
@@ -2432,7 +2458,8 @@
       <c r="H77" s="12" t="n"/>
       <c r="I77" s="12" t="n"/>
       <c r="J77" s="12" t="n"/>
-      <c r="L77" s="13" t="inlineStr">
+      <c r="K77" s="12" t="n"/>
+      <c r="M77" s="13" t="inlineStr">
         <is>
           <t>Set #6</t>
         </is>
@@ -2449,9 +2476,10 @@
       <c r="H78" s="12" t="n"/>
       <c r="I78" s="12" t="n"/>
       <c r="J78" s="12" t="n"/>
-      <c r="L78" s="14" t="n"/>
+      <c r="K78" s="12" t="n"/>
       <c r="M78" s="14" t="n"/>
       <c r="N78" s="14" t="n"/>
+      <c r="O78" s="14" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="12" t="n"/>
@@ -2464,9 +2492,10 @@
       <c r="H79" s="12" t="n"/>
       <c r="I79" s="12" t="n"/>
       <c r="J79" s="12" t="n"/>
-      <c r="L79" s="14" t="n"/>
+      <c r="K79" s="12" t="n"/>
       <c r="M79" s="14" t="n"/>
       <c r="N79" s="14" t="n"/>
+      <c r="O79" s="14" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="12" t="n"/>
@@ -2479,9 +2508,10 @@
       <c r="H80" s="12" t="n"/>
       <c r="I80" s="12" t="n"/>
       <c r="J80" s="12" t="n"/>
-      <c r="L80" s="14" t="n"/>
+      <c r="K80" s="12" t="n"/>
       <c r="M80" s="14" t="n"/>
       <c r="N80" s="14" t="n"/>
+      <c r="O80" s="14" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="12" t="n"/>
@@ -2494,7 +2524,8 @@
       <c r="H81" s="12" t="n"/>
       <c r="I81" s="12" t="n"/>
       <c r="J81" s="12" t="n"/>
-      <c r="L81" s="13" t="inlineStr">
+      <c r="K81" s="12" t="n"/>
+      <c r="M81" s="13" t="inlineStr">
         <is>
           <t>Set #7</t>
         </is>
@@ -2511,9 +2542,10 @@
       <c r="H82" s="12" t="n"/>
       <c r="I82" s="12" t="n"/>
       <c r="J82" s="12" t="n"/>
-      <c r="L82" s="14" t="n"/>
+      <c r="K82" s="12" t="n"/>
       <c r="M82" s="14" t="n"/>
       <c r="N82" s="14" t="n"/>
+      <c r="O82" s="14" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="12" t="n"/>
@@ -2526,9 +2558,10 @@
       <c r="H83" s="12" t="n"/>
       <c r="I83" s="12" t="n"/>
       <c r="J83" s="12" t="n"/>
-      <c r="L83" s="14" t="n"/>
+      <c r="K83" s="12" t="n"/>
       <c r="M83" s="14" t="n"/>
       <c r="N83" s="14" t="n"/>
+      <c r="O83" s="14" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="12" t="n"/>
@@ -2541,9 +2574,10 @@
       <c r="H84" s="12" t="n"/>
       <c r="I84" s="12" t="n"/>
       <c r="J84" s="12" t="n"/>
-      <c r="L84" s="14" t="n"/>
+      <c r="K84" s="12" t="n"/>
       <c r="M84" s="14" t="n"/>
       <c r="N84" s="14" t="n"/>
+      <c r="O84" s="14" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="12" t="n"/>
@@ -2556,7 +2590,8 @@
       <c r="H85" s="12" t="n"/>
       <c r="I85" s="12" t="n"/>
       <c r="J85" s="12" t="n"/>
-      <c r="L85" s="13" t="inlineStr">
+      <c r="K85" s="12" t="n"/>
+      <c r="M85" s="13" t="inlineStr">
         <is>
           <t>Set #8</t>
         </is>
@@ -2573,9 +2608,10 @@
       <c r="H86" s="12" t="n"/>
       <c r="I86" s="12" t="n"/>
       <c r="J86" s="12" t="n"/>
-      <c r="L86" s="14" t="n"/>
+      <c r="K86" s="12" t="n"/>
       <c r="M86" s="14" t="n"/>
       <c r="N86" s="14" t="n"/>
+      <c r="O86" s="14" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="12" t="n"/>
@@ -2588,9 +2624,10 @@
       <c r="H87" s="12" t="n"/>
       <c r="I87" s="12" t="n"/>
       <c r="J87" s="12" t="n"/>
-      <c r="L87" s="14" t="n"/>
+      <c r="K87" s="12" t="n"/>
       <c r="M87" s="14" t="n"/>
       <c r="N87" s="14" t="n"/>
+      <c r="O87" s="14" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="12" t="n"/>
@@ -2603,9 +2640,10 @@
       <c r="H88" s="12" t="n"/>
       <c r="I88" s="12" t="n"/>
       <c r="J88" s="12" t="n"/>
-      <c r="L88" s="14" t="n"/>
+      <c r="K88" s="12" t="n"/>
       <c r="M88" s="14" t="n"/>
       <c r="N88" s="14" t="n"/>
+      <c r="O88" s="14" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="12" t="n"/>
@@ -2618,6 +2656,7 @@
       <c r="H89" s="12" t="n"/>
       <c r="I89" s="12" t="n"/>
       <c r="J89" s="12" t="n"/>
+      <c r="K89" s="12" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="12" t="n"/>
@@ -2630,7 +2669,8 @@
       <c r="H90" s="12" t="n"/>
       <c r="I90" s="12" t="n"/>
       <c r="J90" s="12" t="n"/>
-      <c r="L90" s="2" t="inlineStr">
+      <c r="K90" s="12" t="n"/>
+      <c r="M90" s="2" t="inlineStr">
         <is>
           <t>Album #2</t>
         </is>
@@ -2647,7 +2687,8 @@
       <c r="H91" s="12" t="n"/>
       <c r="I91" s="12" t="n"/>
       <c r="J91" s="12" t="n"/>
-      <c r="L91" s="13" t="inlineStr">
+      <c r="K91" s="12" t="n"/>
+      <c r="M91" s="13" t="inlineStr">
         <is>
           <t>Set #1</t>
         </is>
@@ -2664,9 +2705,10 @@
       <c r="H92" s="12" t="n"/>
       <c r="I92" s="12" t="n"/>
       <c r="J92" s="12" t="n"/>
-      <c r="L92" s="14" t="n"/>
+      <c r="K92" s="12" t="n"/>
       <c r="M92" s="14" t="n"/>
       <c r="N92" s="14" t="n"/>
+      <c r="O92" s="14" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="12" t="n"/>
@@ -2679,9 +2721,10 @@
       <c r="H93" s="12" t="n"/>
       <c r="I93" s="12" t="n"/>
       <c r="J93" s="12" t="n"/>
-      <c r="L93" s="14" t="n"/>
+      <c r="K93" s="12" t="n"/>
       <c r="M93" s="14" t="n"/>
       <c r="N93" s="14" t="n"/>
+      <c r="O93" s="14" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="12" t="n"/>
@@ -2694,9 +2737,10 @@
       <c r="H94" s="12" t="n"/>
       <c r="I94" s="12" t="n"/>
       <c r="J94" s="12" t="n"/>
-      <c r="L94" s="14" t="n"/>
+      <c r="K94" s="12" t="n"/>
       <c r="M94" s="14" t="n"/>
       <c r="N94" s="14" t="n"/>
+      <c r="O94" s="14" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="12" t="n"/>
@@ -2709,7 +2753,8 @@
       <c r="H95" s="12" t="n"/>
       <c r="I95" s="12" t="n"/>
       <c r="J95" s="12" t="n"/>
-      <c r="L95" s="13" t="inlineStr">
+      <c r="K95" s="12" t="n"/>
+      <c r="M95" s="13" t="inlineStr">
         <is>
           <t>Set #2</t>
         </is>
@@ -2726,9 +2771,10 @@
       <c r="H96" s="12" t="n"/>
       <c r="I96" s="12" t="n"/>
       <c r="J96" s="12" t="n"/>
-      <c r="L96" s="14" t="n"/>
+      <c r="K96" s="12" t="n"/>
       <c r="M96" s="14" t="n"/>
       <c r="N96" s="14" t="n"/>
+      <c r="O96" s="14" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="12" t="n"/>
@@ -2741,9 +2787,10 @@
       <c r="H97" s="12" t="n"/>
       <c r="I97" s="12" t="n"/>
       <c r="J97" s="12" t="n"/>
-      <c r="L97" s="14" t="n"/>
+      <c r="K97" s="12" t="n"/>
       <c r="M97" s="14" t="n"/>
       <c r="N97" s="14" t="n"/>
+      <c r="O97" s="14" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="12" t="n"/>
@@ -2756,9 +2803,10 @@
       <c r="H98" s="12" t="n"/>
       <c r="I98" s="12" t="n"/>
       <c r="J98" s="12" t="n"/>
-      <c r="L98" s="14" t="n"/>
+      <c r="K98" s="12" t="n"/>
       <c r="M98" s="14" t="n"/>
       <c r="N98" s="14" t="n"/>
+      <c r="O98" s="14" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="12" t="n"/>
@@ -2771,7 +2819,8 @@
       <c r="H99" s="12" t="n"/>
       <c r="I99" s="12" t="n"/>
       <c r="J99" s="12" t="n"/>
-      <c r="L99" s="13" t="inlineStr">
+      <c r="K99" s="12" t="n"/>
+      <c r="M99" s="13" t="inlineStr">
         <is>
           <t>Set #3</t>
         </is>
@@ -2788,9 +2837,10 @@
       <c r="H100" s="12" t="n"/>
       <c r="I100" s="12" t="n"/>
       <c r="J100" s="12" t="n"/>
-      <c r="L100" s="14" t="n"/>
+      <c r="K100" s="12" t="n"/>
       <c r="M100" s="14" t="n"/>
       <c r="N100" s="14" t="n"/>
+      <c r="O100" s="14" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="12" t="n"/>
@@ -2803,9 +2853,10 @@
       <c r="H101" s="12" t="n"/>
       <c r="I101" s="12" t="n"/>
       <c r="J101" s="12" t="n"/>
-      <c r="L101" s="14" t="n"/>
+      <c r="K101" s="12" t="n"/>
       <c r="M101" s="14" t="n"/>
       <c r="N101" s="14" t="n"/>
+      <c r="O101" s="14" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="12" t="n"/>
@@ -2818,9 +2869,10 @@
       <c r="H102" s="12" t="n"/>
       <c r="I102" s="12" t="n"/>
       <c r="J102" s="12" t="n"/>
-      <c r="L102" s="14" t="n"/>
+      <c r="K102" s="12" t="n"/>
       <c r="M102" s="14" t="n"/>
       <c r="N102" s="14" t="n"/>
+      <c r="O102" s="14" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="12" t="n"/>
@@ -2833,7 +2885,8 @@
       <c r="H103" s="12" t="n"/>
       <c r="I103" s="12" t="n"/>
       <c r="J103" s="12" t="n"/>
-      <c r="L103" s="13" t="inlineStr">
+      <c r="K103" s="12" t="n"/>
+      <c r="M103" s="13" t="inlineStr">
         <is>
           <t>Set #4</t>
         </is>
@@ -2850,9 +2903,10 @@
       <c r="H104" s="12" t="n"/>
       <c r="I104" s="12" t="n"/>
       <c r="J104" s="12" t="n"/>
-      <c r="L104" s="14" t="n"/>
+      <c r="K104" s="12" t="n"/>
       <c r="M104" s="14" t="n"/>
       <c r="N104" s="14" t="n"/>
+      <c r="O104" s="14" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="12" t="n"/>
@@ -2865,9 +2919,10 @@
       <c r="H105" s="12" t="n"/>
       <c r="I105" s="12" t="n"/>
       <c r="J105" s="12" t="n"/>
-      <c r="L105" s="14" t="n"/>
+      <c r="K105" s="12" t="n"/>
       <c r="M105" s="14" t="n"/>
       <c r="N105" s="14" t="n"/>
+      <c r="O105" s="14" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="12" t="n"/>
@@ -2880,9 +2935,10 @@
       <c r="H106" s="12" t="n"/>
       <c r="I106" s="12" t="n"/>
       <c r="J106" s="12" t="n"/>
-      <c r="L106" s="14" t="n"/>
+      <c r="K106" s="12" t="n"/>
       <c r="M106" s="14" t="n"/>
       <c r="N106" s="14" t="n"/>
+      <c r="O106" s="14" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="12" t="n"/>
@@ -2895,7 +2951,8 @@
       <c r="H107" s="12" t="n"/>
       <c r="I107" s="12" t="n"/>
       <c r="J107" s="12" t="n"/>
-      <c r="L107" s="13" t="inlineStr">
+      <c r="K107" s="12" t="n"/>
+      <c r="M107" s="13" t="inlineStr">
         <is>
           <t>Set #5</t>
         </is>
@@ -2912,9 +2969,10 @@
       <c r="H108" s="12" t="n"/>
       <c r="I108" s="12" t="n"/>
       <c r="J108" s="12" t="n"/>
-      <c r="L108" s="14" t="n"/>
+      <c r="K108" s="12" t="n"/>
       <c r="M108" s="14" t="n"/>
       <c r="N108" s="14" t="n"/>
+      <c r="O108" s="14" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="12" t="n"/>
@@ -2927,9 +2985,10 @@
       <c r="H109" s="12" t="n"/>
       <c r="I109" s="12" t="n"/>
       <c r="J109" s="12" t="n"/>
-      <c r="L109" s="14" t="n"/>
+      <c r="K109" s="12" t="n"/>
       <c r="M109" s="14" t="n"/>
       <c r="N109" s="14" t="n"/>
+      <c r="O109" s="14" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="12" t="n"/>
@@ -2942,9 +3001,10 @@
       <c r="H110" s="12" t="n"/>
       <c r="I110" s="12" t="n"/>
       <c r="J110" s="12" t="n"/>
-      <c r="L110" s="14" t="n"/>
+      <c r="K110" s="12" t="n"/>
       <c r="M110" s="14" t="n"/>
       <c r="N110" s="14" t="n"/>
+      <c r="O110" s="14" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="12" t="n"/>
@@ -2957,7 +3017,8 @@
       <c r="H111" s="12" t="n"/>
       <c r="I111" s="12" t="n"/>
       <c r="J111" s="12" t="n"/>
-      <c r="L111" s="13" t="inlineStr">
+      <c r="K111" s="12" t="n"/>
+      <c r="M111" s="13" t="inlineStr">
         <is>
           <t>Set #6</t>
         </is>
@@ -2974,9 +3035,10 @@
       <c r="H112" s="12" t="n"/>
       <c r="I112" s="12" t="n"/>
       <c r="J112" s="12" t="n"/>
-      <c r="L112" s="14" t="n"/>
+      <c r="K112" s="12" t="n"/>
       <c r="M112" s="14" t="n"/>
       <c r="N112" s="14" t="n"/>
+      <c r="O112" s="14" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="12" t="n"/>
@@ -2989,9 +3051,10 @@
       <c r="H113" s="12" t="n"/>
       <c r="I113" s="12" t="n"/>
       <c r="J113" s="12" t="n"/>
-      <c r="L113" s="14" t="n"/>
+      <c r="K113" s="12" t="n"/>
       <c r="M113" s="14" t="n"/>
       <c r="N113" s="14" t="n"/>
+      <c r="O113" s="14" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="12" t="n"/>
@@ -3004,9 +3067,10 @@
       <c r="H114" s="12" t="n"/>
       <c r="I114" s="12" t="n"/>
       <c r="J114" s="12" t="n"/>
-      <c r="L114" s="14" t="n"/>
+      <c r="K114" s="12" t="n"/>
       <c r="M114" s="14" t="n"/>
       <c r="N114" s="14" t="n"/>
+      <c r="O114" s="14" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="12" t="n"/>
@@ -3019,7 +3083,8 @@
       <c r="H115" s="12" t="n"/>
       <c r="I115" s="12" t="n"/>
       <c r="J115" s="12" t="n"/>
-      <c r="L115" s="13" t="inlineStr">
+      <c r="K115" s="12" t="n"/>
+      <c r="M115" s="13" t="inlineStr">
         <is>
           <t>Set #7</t>
         </is>
@@ -3036,9 +3101,10 @@
       <c r="H116" s="12" t="n"/>
       <c r="I116" s="12" t="n"/>
       <c r="J116" s="12" t="n"/>
-      <c r="L116" s="14" t="n"/>
+      <c r="K116" s="12" t="n"/>
       <c r="M116" s="14" t="n"/>
       <c r="N116" s="14" t="n"/>
+      <c r="O116" s="14" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="12" t="n"/>
@@ -3051,9 +3117,10 @@
       <c r="H117" s="12" t="n"/>
       <c r="I117" s="12" t="n"/>
       <c r="J117" s="12" t="n"/>
-      <c r="L117" s="14" t="n"/>
+      <c r="K117" s="12" t="n"/>
       <c r="M117" s="14" t="n"/>
       <c r="N117" s="14" t="n"/>
+      <c r="O117" s="14" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="12" t="n"/>
@@ -3066,9 +3133,10 @@
       <c r="H118" s="12" t="n"/>
       <c r="I118" s="12" t="n"/>
       <c r="J118" s="12" t="n"/>
-      <c r="L118" s="14" t="n"/>
+      <c r="K118" s="12" t="n"/>
       <c r="M118" s="14" t="n"/>
       <c r="N118" s="14" t="n"/>
+      <c r="O118" s="14" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="12" t="n"/>
@@ -3081,7 +3149,8 @@
       <c r="H119" s="12" t="n"/>
       <c r="I119" s="12" t="n"/>
       <c r="J119" s="12" t="n"/>
-      <c r="L119" s="13" t="inlineStr">
+      <c r="K119" s="12" t="n"/>
+      <c r="M119" s="13" t="inlineStr">
         <is>
           <t>Set #8</t>
         </is>
@@ -3098,9 +3167,10 @@
       <c r="H120" s="12" t="n"/>
       <c r="I120" s="12" t="n"/>
       <c r="J120" s="12" t="n"/>
-      <c r="L120" s="14" t="n"/>
+      <c r="K120" s="12" t="n"/>
       <c r="M120" s="14" t="n"/>
       <c r="N120" s="14" t="n"/>
+      <c r="O120" s="14" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="12" t="n"/>
@@ -3113,9 +3183,10 @@
       <c r="H121" s="12" t="n"/>
       <c r="I121" s="12" t="n"/>
       <c r="J121" s="12" t="n"/>
-      <c r="L121" s="14" t="n"/>
+      <c r="K121" s="12" t="n"/>
       <c r="M121" s="14" t="n"/>
       <c r="N121" s="14" t="n"/>
+      <c r="O121" s="14" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="12" t="n"/>
@@ -3128,9 +3199,10 @@
       <c r="H122" s="12" t="n"/>
       <c r="I122" s="12" t="n"/>
       <c r="J122" s="12" t="n"/>
-      <c r="L122" s="14" t="n"/>
+      <c r="K122" s="12" t="n"/>
       <c r="M122" s="14" t="n"/>
       <c r="N122" s="14" t="n"/>
+      <c r="O122" s="14" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="12" t="n"/>
@@ -3143,6 +3215,7 @@
       <c r="H123" s="12" t="n"/>
       <c r="I123" s="12" t="n"/>
       <c r="J123" s="12" t="n"/>
+      <c r="K123" s="12" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="12" t="n"/>
@@ -3155,7 +3228,8 @@
       <c r="H124" s="12" t="n"/>
       <c r="I124" s="12" t="n"/>
       <c r="J124" s="12" t="n"/>
-      <c r="L124" s="2" t="inlineStr">
+      <c r="K124" s="12" t="n"/>
+      <c r="M124" s="2" t="inlineStr">
         <is>
           <t>Album #3</t>
         </is>
@@ -3172,7 +3246,8 @@
       <c r="H125" s="12" t="n"/>
       <c r="I125" s="12" t="n"/>
       <c r="J125" s="12" t="n"/>
-      <c r="L125" s="13" t="inlineStr">
+      <c r="K125" s="12" t="n"/>
+      <c r="M125" s="13" t="inlineStr">
         <is>
           <t>Set #1</t>
         </is>
@@ -3189,9 +3264,10 @@
       <c r="H126" s="12" t="n"/>
       <c r="I126" s="12" t="n"/>
       <c r="J126" s="12" t="n"/>
-      <c r="L126" s="14" t="n"/>
+      <c r="K126" s="12" t="n"/>
       <c r="M126" s="14" t="n"/>
       <c r="N126" s="14" t="n"/>
+      <c r="O126" s="14" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="12" t="n"/>
@@ -3204,9 +3280,10 @@
       <c r="H127" s="12" t="n"/>
       <c r="I127" s="12" t="n"/>
       <c r="J127" s="12" t="n"/>
-      <c r="L127" s="14" t="n"/>
+      <c r="K127" s="12" t="n"/>
       <c r="M127" s="14" t="n"/>
       <c r="N127" s="14" t="n"/>
+      <c r="O127" s="14" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="12" t="n"/>
@@ -3219,9 +3296,10 @@
       <c r="H128" s="12" t="n"/>
       <c r="I128" s="12" t="n"/>
       <c r="J128" s="12" t="n"/>
-      <c r="L128" s="14" t="n"/>
+      <c r="K128" s="12" t="n"/>
       <c r="M128" s="14" t="n"/>
       <c r="N128" s="14" t="n"/>
+      <c r="O128" s="14" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="12" t="n"/>
@@ -3234,7 +3312,8 @@
       <c r="H129" s="12" t="n"/>
       <c r="I129" s="12" t="n"/>
       <c r="J129" s="12" t="n"/>
-      <c r="L129" s="13" t="inlineStr">
+      <c r="K129" s="12" t="n"/>
+      <c r="M129" s="13" t="inlineStr">
         <is>
           <t>Set #2</t>
         </is>
@@ -3251,9 +3330,10 @@
       <c r="H130" s="12" t="n"/>
       <c r="I130" s="12" t="n"/>
       <c r="J130" s="12" t="n"/>
-      <c r="L130" s="14" t="n"/>
+      <c r="K130" s="12" t="n"/>
       <c r="M130" s="14" t="n"/>
       <c r="N130" s="14" t="n"/>
+      <c r="O130" s="14" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="12" t="n"/>
@@ -3266,9 +3346,10 @@
       <c r="H131" s="12" t="n"/>
       <c r="I131" s="12" t="n"/>
       <c r="J131" s="12" t="n"/>
-      <c r="L131" s="14" t="n"/>
+      <c r="K131" s="12" t="n"/>
       <c r="M131" s="14" t="n"/>
       <c r="N131" s="14" t="n"/>
+      <c r="O131" s="14" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="12" t="n"/>
@@ -3281,9 +3362,10 @@
       <c r="H132" s="12" t="n"/>
       <c r="I132" s="12" t="n"/>
       <c r="J132" s="12" t="n"/>
-      <c r="L132" s="14" t="n"/>
+      <c r="K132" s="12" t="n"/>
       <c r="M132" s="14" t="n"/>
       <c r="N132" s="14" t="n"/>
+      <c r="O132" s="14" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="12" t="n"/>
@@ -3296,7 +3378,8 @@
       <c r="H133" s="12" t="n"/>
       <c r="I133" s="12" t="n"/>
       <c r="J133" s="12" t="n"/>
-      <c r="L133" s="13" t="inlineStr">
+      <c r="K133" s="12" t="n"/>
+      <c r="M133" s="13" t="inlineStr">
         <is>
           <t>Set #3</t>
         </is>
@@ -3313,9 +3396,10 @@
       <c r="H134" s="12" t="n"/>
       <c r="I134" s="12" t="n"/>
       <c r="J134" s="12" t="n"/>
-      <c r="L134" s="14" t="n"/>
+      <c r="K134" s="12" t="n"/>
       <c r="M134" s="14" t="n"/>
       <c r="N134" s="14" t="n"/>
+      <c r="O134" s="14" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="12" t="n"/>
@@ -3328,9 +3412,10 @@
       <c r="H135" s="12" t="n"/>
       <c r="I135" s="12" t="n"/>
       <c r="J135" s="12" t="n"/>
-      <c r="L135" s="14" t="n"/>
+      <c r="K135" s="12" t="n"/>
       <c r="M135" s="14" t="n"/>
       <c r="N135" s="14" t="n"/>
+      <c r="O135" s="14" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="12" t="n"/>
@@ -3343,9 +3428,10 @@
       <c r="H136" s="12" t="n"/>
       <c r="I136" s="12" t="n"/>
       <c r="J136" s="12" t="n"/>
-      <c r="L136" s="14" t="n"/>
+      <c r="K136" s="12" t="n"/>
       <c r="M136" s="14" t="n"/>
       <c r="N136" s="14" t="n"/>
+      <c r="O136" s="14" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="12" t="n"/>
@@ -3358,7 +3444,8 @@
       <c r="H137" s="12" t="n"/>
       <c r="I137" s="12" t="n"/>
       <c r="J137" s="12" t="n"/>
-      <c r="L137" s="13" t="inlineStr">
+      <c r="K137" s="12" t="n"/>
+      <c r="M137" s="13" t="inlineStr">
         <is>
           <t>Set #4</t>
         </is>
@@ -3375,9 +3462,10 @@
       <c r="H138" s="12" t="n"/>
       <c r="I138" s="12" t="n"/>
       <c r="J138" s="12" t="n"/>
-      <c r="L138" s="14" t="n"/>
+      <c r="K138" s="12" t="n"/>
       <c r="M138" s="14" t="n"/>
       <c r="N138" s="14" t="n"/>
+      <c r="O138" s="14" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="12" t="n"/>
@@ -3390,9 +3478,10 @@
       <c r="H139" s="12" t="n"/>
       <c r="I139" s="12" t="n"/>
       <c r="J139" s="12" t="n"/>
-      <c r="L139" s="14" t="n"/>
+      <c r="K139" s="12" t="n"/>
       <c r="M139" s="14" t="n"/>
       <c r="N139" s="14" t="n"/>
+      <c r="O139" s="14" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="12" t="n"/>
@@ -3405,9 +3494,10 @@
       <c r="H140" s="12" t="n"/>
       <c r="I140" s="12" t="n"/>
       <c r="J140" s="12" t="n"/>
-      <c r="L140" s="14" t="n"/>
+      <c r="K140" s="12" t="n"/>
       <c r="M140" s="14" t="n"/>
       <c r="N140" s="14" t="n"/>
+      <c r="O140" s="14" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="12" t="n"/>
@@ -3420,7 +3510,8 @@
       <c r="H141" s="12" t="n"/>
       <c r="I141" s="12" t="n"/>
       <c r="J141" s="12" t="n"/>
-      <c r="L141" s="13" t="inlineStr">
+      <c r="K141" s="12" t="n"/>
+      <c r="M141" s="13" t="inlineStr">
         <is>
           <t>Set #5</t>
         </is>
@@ -3437,9 +3528,10 @@
       <c r="H142" s="12" t="n"/>
       <c r="I142" s="12" t="n"/>
       <c r="J142" s="12" t="n"/>
-      <c r="L142" s="14" t="n"/>
+      <c r="K142" s="12" t="n"/>
       <c r="M142" s="14" t="n"/>
       <c r="N142" s="14" t="n"/>
+      <c r="O142" s="14" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="12" t="n"/>
@@ -3452,9 +3544,10 @@
       <c r="H143" s="12" t="n"/>
       <c r="I143" s="12" t="n"/>
       <c r="J143" s="12" t="n"/>
-      <c r="L143" s="14" t="n"/>
+      <c r="K143" s="12" t="n"/>
       <c r="M143" s="14" t="n"/>
       <c r="N143" s="14" t="n"/>
+      <c r="O143" s="14" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="12" t="n"/>
@@ -3467,9 +3560,10 @@
       <c r="H144" s="12" t="n"/>
       <c r="I144" s="12" t="n"/>
       <c r="J144" s="12" t="n"/>
-      <c r="L144" s="14" t="n"/>
+      <c r="K144" s="12" t="n"/>
       <c r="M144" s="14" t="n"/>
       <c r="N144" s="14" t="n"/>
+      <c r="O144" s="14" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="12" t="n"/>
@@ -3482,7 +3576,8 @@
       <c r="H145" s="12" t="n"/>
       <c r="I145" s="12" t="n"/>
       <c r="J145" s="12" t="n"/>
-      <c r="L145" s="13" t="inlineStr">
+      <c r="K145" s="12" t="n"/>
+      <c r="M145" s="13" t="inlineStr">
         <is>
           <t>Set #6</t>
         </is>
@@ -3499,9 +3594,10 @@
       <c r="H146" s="12" t="n"/>
       <c r="I146" s="12" t="n"/>
       <c r="J146" s="12" t="n"/>
-      <c r="L146" s="14" t="n"/>
+      <c r="K146" s="12" t="n"/>
       <c r="M146" s="14" t="n"/>
       <c r="N146" s="14" t="n"/>
+      <c r="O146" s="14" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="12" t="n"/>
@@ -3514,9 +3610,10 @@
       <c r="H147" s="12" t="n"/>
       <c r="I147" s="12" t="n"/>
       <c r="J147" s="12" t="n"/>
-      <c r="L147" s="14" t="n"/>
+      <c r="K147" s="12" t="n"/>
       <c r="M147" s="14" t="n"/>
       <c r="N147" s="14" t="n"/>
+      <c r="O147" s="14" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="12" t="n"/>
@@ -3529,9 +3626,10 @@
       <c r="H148" s="12" t="n"/>
       <c r="I148" s="12" t="n"/>
       <c r="J148" s="12" t="n"/>
-      <c r="L148" s="14" t="n"/>
+      <c r="K148" s="12" t="n"/>
       <c r="M148" s="14" t="n"/>
       <c r="N148" s="14" t="n"/>
+      <c r="O148" s="14" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="12" t="n"/>
@@ -3544,7 +3642,8 @@
       <c r="H149" s="12" t="n"/>
       <c r="I149" s="12" t="n"/>
       <c r="J149" s="12" t="n"/>
-      <c r="L149" s="13" t="inlineStr">
+      <c r="K149" s="12" t="n"/>
+      <c r="M149" s="13" t="inlineStr">
         <is>
           <t>Set #7</t>
         </is>
@@ -3561,9 +3660,10 @@
       <c r="H150" s="12" t="n"/>
       <c r="I150" s="12" t="n"/>
       <c r="J150" s="12" t="n"/>
-      <c r="L150" s="14" t="n"/>
+      <c r="K150" s="12" t="n"/>
       <c r="M150" s="14" t="n"/>
       <c r="N150" s="14" t="n"/>
+      <c r="O150" s="14" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="12" t="n"/>
@@ -3576,9 +3676,10 @@
       <c r="H151" s="12" t="n"/>
       <c r="I151" s="12" t="n"/>
       <c r="J151" s="12" t="n"/>
-      <c r="L151" s="14" t="n"/>
+      <c r="K151" s="12" t="n"/>
       <c r="M151" s="14" t="n"/>
       <c r="N151" s="14" t="n"/>
+      <c r="O151" s="14" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="12" t="n"/>
@@ -3591,9 +3692,10 @@
       <c r="H152" s="12" t="n"/>
       <c r="I152" s="12" t="n"/>
       <c r="J152" s="12" t="n"/>
-      <c r="L152" s="14" t="n"/>
+      <c r="K152" s="12" t="n"/>
       <c r="M152" s="14" t="n"/>
       <c r="N152" s="14" t="n"/>
+      <c r="O152" s="14" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="12" t="n"/>
@@ -3606,7 +3708,8 @@
       <c r="H153" s="12" t="n"/>
       <c r="I153" s="12" t="n"/>
       <c r="J153" s="12" t="n"/>
-      <c r="L153" s="13" t="inlineStr">
+      <c r="K153" s="12" t="n"/>
+      <c r="M153" s="13" t="inlineStr">
         <is>
           <t>Set #8</t>
         </is>
@@ -3623,9 +3726,10 @@
       <c r="H154" s="12" t="n"/>
       <c r="I154" s="12" t="n"/>
       <c r="J154" s="12" t="n"/>
-      <c r="L154" s="14" t="n"/>
+      <c r="K154" s="12" t="n"/>
       <c r="M154" s="14" t="n"/>
       <c r="N154" s="14" t="n"/>
+      <c r="O154" s="14" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="12" t="n"/>
@@ -3638,9 +3742,10 @@
       <c r="H155" s="12" t="n"/>
       <c r="I155" s="12" t="n"/>
       <c r="J155" s="12" t="n"/>
-      <c r="L155" s="14" t="n"/>
+      <c r="K155" s="12" t="n"/>
       <c r="M155" s="14" t="n"/>
       <c r="N155" s="14" t="n"/>
+      <c r="O155" s="14" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="12" t="n"/>
@@ -3653,9 +3758,10 @@
       <c r="H156" s="12" t="n"/>
       <c r="I156" s="12" t="n"/>
       <c r="J156" s="12" t="n"/>
-      <c r="L156" s="14" t="n"/>
+      <c r="K156" s="12" t="n"/>
       <c r="M156" s="14" t="n"/>
       <c r="N156" s="14" t="n"/>
+      <c r="O156" s="14" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="12" t="n"/>
@@ -3668,6 +3774,7 @@
       <c r="H157" s="12" t="n"/>
       <c r="I157" s="12" t="n"/>
       <c r="J157" s="12" t="n"/>
+      <c r="K157" s="12" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="12" t="n"/>
@@ -3680,6 +3787,7 @@
       <c r="H158" s="12" t="n"/>
       <c r="I158" s="12" t="n"/>
       <c r="J158" s="12" t="n"/>
+      <c r="K158" s="12" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="15" t="inlineStr">
@@ -3696,6 +3804,7 @@
       <c r="H159" s="12" t="n"/>
       <c r="I159" s="12" t="n"/>
       <c r="J159" s="12" t="n"/>
+      <c r="K159" s="12" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
@@ -3712,6 +3821,7 @@
       <c r="H160" s="12" t="n"/>
       <c r="I160" s="12" t="n"/>
       <c r="J160" s="12" t="n"/>
+      <c r="K160" s="12" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
@@ -3728,6 +3838,7 @@
       <c r="H161" s="12" t="n"/>
       <c r="I161" s="12" t="n"/>
       <c r="J161" s="12" t="n"/>
+      <c r="K161" s="12" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
@@ -3744,6 +3855,7 @@
       <c r="H162" s="12" t="n"/>
       <c r="I162" s="12" t="n"/>
       <c r="J162" s="12" t="n"/>
+      <c r="K162" s="12" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
@@ -3760,6 +3872,7 @@
       <c r="H163" s="12" t="n"/>
       <c r="I163" s="12" t="n"/>
       <c r="J163" s="12" t="n"/>
+      <c r="K163" s="12" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="12" t="n"/>
@@ -3772,6 +3885,7 @@
       <c r="H164" s="12" t="n"/>
       <c r="I164" s="12" t="n"/>
       <c r="J164" s="12" t="n"/>
+      <c r="K164" s="12" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="12" t="n"/>
@@ -3784,6 +3898,7 @@
       <c r="H165" s="12" t="n"/>
       <c r="I165" s="12" t="n"/>
       <c r="J165" s="12" t="n"/>
+      <c r="K165" s="12" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="12" t="n"/>
@@ -3796,6 +3911,7 @@
       <c r="H166" s="12" t="n"/>
       <c r="I166" s="12" t="n"/>
       <c r="J166" s="12" t="n"/>
+      <c r="K166" s="12" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="12" t="n"/>
@@ -3808,6 +3924,7 @@
       <c r="H167" s="12" t="n"/>
       <c r="I167" s="12" t="n"/>
       <c r="J167" s="12" t="n"/>
+      <c r="K167" s="12" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="12" t="n"/>
@@ -3820,6 +3937,7 @@
       <c r="H168" s="12" t="n"/>
       <c r="I168" s="12" t="n"/>
       <c r="J168" s="12" t="n"/>
+      <c r="K168" s="12" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="12" t="n"/>
@@ -3832,6 +3950,7 @@
       <c r="H169" s="12" t="n"/>
       <c r="I169" s="12" t="n"/>
       <c r="J169" s="12" t="n"/>
+      <c r="K169" s="12" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="12" t="n"/>
@@ -3844,6 +3963,7 @@
       <c r="H170" s="12" t="n"/>
       <c r="I170" s="12" t="n"/>
       <c r="J170" s="12" t="n"/>
+      <c r="K170" s="12" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="12" t="n"/>
@@ -3856,6 +3976,7 @@
       <c r="H171" s="12" t="n"/>
       <c r="I171" s="12" t="n"/>
       <c r="J171" s="12" t="n"/>
+      <c r="K171" s="12" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="12" t="n"/>
@@ -3868,6 +3989,7 @@
       <c r="H172" s="12" t="n"/>
       <c r="I172" s="12" t="n"/>
       <c r="J172" s="12" t="n"/>
+      <c r="K172" s="12" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="12" t="n"/>
@@ -3880,6 +4002,7 @@
       <c r="H173" s="12" t="n"/>
       <c r="I173" s="12" t="n"/>
       <c r="J173" s="12" t="n"/>
+      <c r="K173" s="12" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="12" t="n"/>
@@ -3892,6 +4015,7 @@
       <c r="H174" s="12" t="n"/>
       <c r="I174" s="12" t="n"/>
       <c r="J174" s="12" t="n"/>
+      <c r="K174" s="12" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="12" t="n"/>
@@ -3904,6 +4028,7 @@
       <c r="H175" s="12" t="n"/>
       <c r="I175" s="12" t="n"/>
       <c r="J175" s="12" t="n"/>
+      <c r="K175" s="12" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="12" t="n"/>
@@ -3916,6 +4041,7 @@
       <c r="H176" s="12" t="n"/>
       <c r="I176" s="12" t="n"/>
       <c r="J176" s="12" t="n"/>
+      <c r="K176" s="12" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="12" t="n"/>
@@ -3928,6 +4054,7 @@
       <c r="H177" s="12" t="n"/>
       <c r="I177" s="12" t="n"/>
       <c r="J177" s="12" t="n"/>
+      <c r="K177" s="12" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="12" t="n"/>
@@ -3940,6 +4067,7 @@
       <c r="H178" s="12" t="n"/>
       <c r="I178" s="12" t="n"/>
       <c r="J178" s="12" t="n"/>
+      <c r="K178" s="12" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="12" t="n"/>
@@ -3952,6 +4080,7 @@
       <c r="H179" s="12" t="n"/>
       <c r="I179" s="12" t="n"/>
       <c r="J179" s="12" t="n"/>
+      <c r="K179" s="12" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="12" t="n"/>
@@ -3964,6 +4093,7 @@
       <c r="H180" s="12" t="n"/>
       <c r="I180" s="12" t="n"/>
       <c r="J180" s="12" t="n"/>
+      <c r="K180" s="12" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="12" t="n"/>
@@ -3976,6 +4106,7 @@
       <c r="H181" s="12" t="n"/>
       <c r="I181" s="12" t="n"/>
       <c r="J181" s="12" t="n"/>
+      <c r="K181" s="12" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="12" t="n"/>
@@ -3988,6 +4119,7 @@
       <c r="H182" s="12" t="n"/>
       <c r="I182" s="12" t="n"/>
       <c r="J182" s="12" t="n"/>
+      <c r="K182" s="12" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="12" t="n"/>
@@ -4000,6 +4132,7 @@
       <c r="H183" s="12" t="n"/>
       <c r="I183" s="12" t="n"/>
       <c r="J183" s="12" t="n"/>
+      <c r="K183" s="12" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="12" t="n"/>
@@ -4012,6 +4145,7 @@
       <c r="H184" s="12" t="n"/>
       <c r="I184" s="12" t="n"/>
       <c r="J184" s="12" t="n"/>
+      <c r="K184" s="12" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="12" t="n"/>
@@ -4024,6 +4158,7 @@
       <c r="H185" s="12" t="n"/>
       <c r="I185" s="12" t="n"/>
       <c r="J185" s="12" t="n"/>
+      <c r="K185" s="12" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="12" t="n"/>
@@ -4036,6 +4171,7 @@
       <c r="H186" s="12" t="n"/>
       <c r="I186" s="12" t="n"/>
       <c r="J186" s="12" t="n"/>
+      <c r="K186" s="12" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="12" t="n"/>
@@ -4048,6 +4184,7 @@
       <c r="H187" s="12" t="n"/>
       <c r="I187" s="12" t="n"/>
       <c r="J187" s="12" t="n"/>
+      <c r="K187" s="12" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="12" t="n"/>
@@ -4060,6 +4197,7 @@
       <c r="H188" s="12" t="n"/>
       <c r="I188" s="12" t="n"/>
       <c r="J188" s="12" t="n"/>
+      <c r="K188" s="12" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="12" t="n"/>
@@ -4072,6 +4210,7 @@
       <c r="H189" s="12" t="n"/>
       <c r="I189" s="12" t="n"/>
       <c r="J189" s="12" t="n"/>
+      <c r="K189" s="12" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="12" t="n"/>
@@ -4084,6 +4223,7 @@
       <c r="H190" s="12" t="n"/>
       <c r="I190" s="12" t="n"/>
       <c r="J190" s="12" t="n"/>
+      <c r="K190" s="12" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="12" t="n"/>
@@ -4096,6 +4236,7 @@
       <c r="H191" s="12" t="n"/>
       <c r="I191" s="12" t="n"/>
       <c r="J191" s="12" t="n"/>
+      <c r="K191" s="12" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="12" t="n"/>
@@ -4108,6 +4249,7 @@
       <c r="H192" s="12" t="n"/>
       <c r="I192" s="12" t="n"/>
       <c r="J192" s="12" t="n"/>
+      <c r="K192" s="12" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="12" t="n"/>
@@ -4120,6 +4262,7 @@
       <c r="H193" s="12" t="n"/>
       <c r="I193" s="12" t="n"/>
       <c r="J193" s="12" t="n"/>
+      <c r="K193" s="12" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="12" t="n"/>
@@ -4132,6 +4275,7 @@
       <c r="H194" s="12" t="n"/>
       <c r="I194" s="12" t="n"/>
       <c r="J194" s="12" t="n"/>
+      <c r="K194" s="12" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="12" t="n"/>
@@ -4144,6 +4288,7 @@
       <c r="H195" s="12" t="n"/>
       <c r="I195" s="12" t="n"/>
       <c r="J195" s="12" t="n"/>
+      <c r="K195" s="12" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="12" t="n"/>
@@ -4156,6 +4301,7 @@
       <c r="H196" s="12" t="n"/>
       <c r="I196" s="12" t="n"/>
       <c r="J196" s="12" t="n"/>
+      <c r="K196" s="12" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="12" t="n"/>
@@ -4168,6 +4314,7 @@
       <c r="H197" s="12" t="n"/>
       <c r="I197" s="12" t="n"/>
       <c r="J197" s="12" t="n"/>
+      <c r="K197" s="12" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="12" t="n"/>
@@ -4180,6 +4327,7 @@
       <c r="H198" s="12" t="n"/>
       <c r="I198" s="12" t="n"/>
       <c r="J198" s="12" t="n"/>
+      <c r="K198" s="12" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="12" t="n"/>
@@ -4192,6 +4340,7 @@
       <c r="H199" s="12" t="n"/>
       <c r="I199" s="12" t="n"/>
       <c r="J199" s="12" t="n"/>
+      <c r="K199" s="12" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="12" t="n"/>
@@ -4204,6 +4353,7 @@
       <c r="H200" s="12" t="n"/>
       <c r="I200" s="12" t="n"/>
       <c r="J200" s="12" t="n"/>
+      <c r="K200" s="12" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="12" t="n"/>
@@ -4216,6 +4366,7 @@
       <c r="H201" s="12" t="n"/>
       <c r="I201" s="12" t="n"/>
       <c r="J201" s="12" t="n"/>
+      <c r="K201" s="12" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="12" t="n"/>
@@ -4228,6 +4379,7 @@
       <c r="H202" s="12" t="n"/>
       <c r="I202" s="12" t="n"/>
       <c r="J202" s="12" t="n"/>
+      <c r="K202" s="12" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="12" t="n"/>
@@ -4240,6 +4392,7 @@
       <c r="H203" s="12" t="n"/>
       <c r="I203" s="12" t="n"/>
       <c r="J203" s="12" t="n"/>
+      <c r="K203" s="12" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="12" t="n"/>
@@ -4252,6 +4405,7 @@
       <c r="H204" s="12" t="n"/>
       <c r="I204" s="12" t="n"/>
       <c r="J204" s="12" t="n"/>
+      <c r="K204" s="12" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="12" t="n"/>
@@ -4264,6 +4418,7 @@
       <c r="H205" s="12" t="n"/>
       <c r="I205" s="12" t="n"/>
       <c r="J205" s="12" t="n"/>
+      <c r="K205" s="12" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="12" t="n"/>
@@ -4276,6 +4431,7 @@
       <c r="H206" s="12" t="n"/>
       <c r="I206" s="12" t="n"/>
       <c r="J206" s="12" t="n"/>
+      <c r="K206" s="12" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="12" t="n"/>
@@ -4288,6 +4444,7 @@
       <c r="H207" s="12" t="n"/>
       <c r="I207" s="12" t="n"/>
       <c r="J207" s="12" t="n"/>
+      <c r="K207" s="12" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="12" t="n"/>
@@ -4300,6 +4457,7 @@
       <c r="H208" s="12" t="n"/>
       <c r="I208" s="12" t="n"/>
       <c r="J208" s="12" t="n"/>
+      <c r="K208" s="12" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="12" t="n"/>
@@ -4312,6 +4470,7 @@
       <c r="H209" s="12" t="n"/>
       <c r="I209" s="12" t="n"/>
       <c r="J209" s="12" t="n"/>
+      <c r="K209" s="12" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="12" t="n"/>
@@ -4324,6 +4483,7 @@
       <c r="H210" s="12" t="n"/>
       <c r="I210" s="12" t="n"/>
       <c r="J210" s="12" t="n"/>
+      <c r="K210" s="12" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="12" t="n"/>
@@ -4336,6 +4496,7 @@
       <c r="H211" s="12" t="n"/>
       <c r="I211" s="12" t="n"/>
       <c r="J211" s="12" t="n"/>
+      <c r="K211" s="12" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="12" t="n"/>
@@ -4348,6 +4509,7 @@
       <c r="H212" s="12" t="n"/>
       <c r="I212" s="12" t="n"/>
       <c r="J212" s="12" t="n"/>
+      <c r="K212" s="12" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="12" t="n"/>
@@ -4360,6 +4522,7 @@
       <c r="H213" s="12" t="n"/>
       <c r="I213" s="12" t="n"/>
       <c r="J213" s="12" t="n"/>
+      <c r="K213" s="12" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="12" t="n"/>
@@ -4372,6 +4535,7 @@
       <c r="H214" s="12" t="n"/>
       <c r="I214" s="12" t="n"/>
       <c r="J214" s="12" t="n"/>
+      <c r="K214" s="12" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="12" t="n"/>
@@ -4384,6 +4548,7 @@
       <c r="H215" s="12" t="n"/>
       <c r="I215" s="12" t="n"/>
       <c r="J215" s="12" t="n"/>
+      <c r="K215" s="12" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="12" t="n"/>
@@ -4396,6 +4561,7 @@
       <c r="H216" s="12" t="n"/>
       <c r="I216" s="12" t="n"/>
       <c r="J216" s="12" t="n"/>
+      <c r="K216" s="12" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="12" t="n"/>
@@ -4408,6 +4574,7 @@
       <c r="H217" s="12" t="n"/>
       <c r="I217" s="12" t="n"/>
       <c r="J217" s="12" t="n"/>
+      <c r="K217" s="12" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="12" t="n"/>
@@ -4420,6 +4587,7 @@
       <c r="H218" s="12" t="n"/>
       <c r="I218" s="12" t="n"/>
       <c r="J218" s="12" t="n"/>
+      <c r="K218" s="12" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="12" t="n"/>
@@ -4432,6 +4600,7 @@
       <c r="H219" s="12" t="n"/>
       <c r="I219" s="12" t="n"/>
       <c r="J219" s="12" t="n"/>
+      <c r="K219" s="12" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="12" t="n"/>
@@ -4444,6 +4613,7 @@
       <c r="H220" s="12" t="n"/>
       <c r="I220" s="12" t="n"/>
       <c r="J220" s="12" t="n"/>
+      <c r="K220" s="12" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="12" t="n"/>
@@ -4456,6 +4626,7 @@
       <c r="H221" s="12" t="n"/>
       <c r="I221" s="12" t="n"/>
       <c r="J221" s="12" t="n"/>
+      <c r="K221" s="12" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="12" t="n"/>
@@ -4468,6 +4639,7 @@
       <c r="H222" s="12" t="n"/>
       <c r="I222" s="12" t="n"/>
       <c r="J222" s="12" t="n"/>
+      <c r="K222" s="12" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="12" t="n"/>
@@ -4480,6 +4652,7 @@
       <c r="H223" s="12" t="n"/>
       <c r="I223" s="12" t="n"/>
       <c r="J223" s="12" t="n"/>
+      <c r="K223" s="12" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="12" t="n"/>
@@ -4492,6 +4665,7 @@
       <c r="H224" s="12" t="n"/>
       <c r="I224" s="12" t="n"/>
       <c r="J224" s="12" t="n"/>
+      <c r="K224" s="12" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="12" t="n"/>
@@ -4504,6 +4678,7 @@
       <c r="H225" s="12" t="n"/>
       <c r="I225" s="12" t="n"/>
       <c r="J225" s="12" t="n"/>
+      <c r="K225" s="12" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="12" t="n"/>
@@ -4516,6 +4691,7 @@
       <c r="H226" s="12" t="n"/>
       <c r="I226" s="12" t="n"/>
       <c r="J226" s="12" t="n"/>
+      <c r="K226" s="12" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="12" t="n"/>
@@ -4528,6 +4704,7 @@
       <c r="H227" s="12" t="n"/>
       <c r="I227" s="12" t="n"/>
       <c r="J227" s="12" t="n"/>
+      <c r="K227" s="12" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="12" t="n"/>
@@ -4540,6 +4717,7 @@
       <c r="H228" s="12" t="n"/>
       <c r="I228" s="12" t="n"/>
       <c r="J228" s="12" t="n"/>
+      <c r="K228" s="12" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="12" t="n"/>
@@ -4552,6 +4730,7 @@
       <c r="H229" s="12" t="n"/>
       <c r="I229" s="12" t="n"/>
       <c r="J229" s="12" t="n"/>
+      <c r="K229" s="12" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="12" t="n"/>
@@ -4564,6 +4743,7 @@
       <c r="H230" s="12" t="n"/>
       <c r="I230" s="12" t="n"/>
       <c r="J230" s="12" t="n"/>
+      <c r="K230" s="12" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="12" t="n"/>
@@ -4576,6 +4756,7 @@
       <c r="H231" s="12" t="n"/>
       <c r="I231" s="12" t="n"/>
       <c r="J231" s="12" t="n"/>
+      <c r="K231" s="12" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="12" t="n"/>
@@ -4588,6 +4769,7 @@
       <c r="H232" s="12" t="n"/>
       <c r="I232" s="12" t="n"/>
       <c r="J232" s="12" t="n"/>
+      <c r="K232" s="12" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="12" t="n"/>
@@ -4600,6 +4782,7 @@
       <c r="H233" s="12" t="n"/>
       <c r="I233" s="12" t="n"/>
       <c r="J233" s="12" t="n"/>
+      <c r="K233" s="12" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="12" t="n"/>
@@ -4612,6 +4795,7 @@
       <c r="H234" s="12" t="n"/>
       <c r="I234" s="12" t="n"/>
       <c r="J234" s="12" t="n"/>
+      <c r="K234" s="12" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="12" t="n"/>
@@ -4624,6 +4808,7 @@
       <c r="H235" s="12" t="n"/>
       <c r="I235" s="12" t="n"/>
       <c r="J235" s="12" t="n"/>
+      <c r="K235" s="12" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="12" t="n"/>
@@ -4636,6 +4821,7 @@
       <c r="H236" s="12" t="n"/>
       <c r="I236" s="12" t="n"/>
       <c r="J236" s="12" t="n"/>
+      <c r="K236" s="12" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="12" t="n"/>
@@ -4648,6 +4834,7 @@
       <c r="H237" s="12" t="n"/>
       <c r="I237" s="12" t="n"/>
       <c r="J237" s="12" t="n"/>
+      <c r="K237" s="12" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="12" t="n"/>
@@ -4660,6 +4847,7 @@
       <c r="H238" s="12" t="n"/>
       <c r="I238" s="12" t="n"/>
       <c r="J238" s="12" t="n"/>
+      <c r="K238" s="12" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="12" t="n"/>
@@ -4672,6 +4860,7 @@
       <c r="H239" s="12" t="n"/>
       <c r="I239" s="12" t="n"/>
       <c r="J239" s="12" t="n"/>
+      <c r="K239" s="12" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="12" t="n"/>
@@ -4684,6 +4873,7 @@
       <c r="H240" s="12" t="n"/>
       <c r="I240" s="12" t="n"/>
       <c r="J240" s="12" t="n"/>
+      <c r="K240" s="12" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="12" t="n"/>
@@ -4696,6 +4886,7 @@
       <c r="H241" s="12" t="n"/>
       <c r="I241" s="12" t="n"/>
       <c r="J241" s="12" t="n"/>
+      <c r="K241" s="12" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="12" t="n"/>
@@ -4708,6 +4899,7 @@
       <c r="H242" s="12" t="n"/>
       <c r="I242" s="12" t="n"/>
       <c r="J242" s="12" t="n"/>
+      <c r="K242" s="12" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="12" t="n"/>
@@ -4720,6 +4912,7 @@
       <c r="H243" s="12" t="n"/>
       <c r="I243" s="12" t="n"/>
       <c r="J243" s="12" t="n"/>
+      <c r="K243" s="12" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="12" t="n"/>
@@ -4732,6 +4925,7 @@
       <c r="H244" s="12" t="n"/>
       <c r="I244" s="12" t="n"/>
       <c r="J244" s="12" t="n"/>
+      <c r="K244" s="12" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="12" t="n"/>
@@ -4744,6 +4938,7 @@
       <c r="H245" s="12" t="n"/>
       <c r="I245" s="12" t="n"/>
       <c r="J245" s="12" t="n"/>
+      <c r="K245" s="12" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="12" t="n"/>
@@ -4756,6 +4951,7 @@
       <c r="H246" s="12" t="n"/>
       <c r="I246" s="12" t="n"/>
       <c r="J246" s="12" t="n"/>
+      <c r="K246" s="12" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="12" t="n"/>
@@ -4768,6 +4964,7 @@
       <c r="H247" s="12" t="n"/>
       <c r="I247" s="12" t="n"/>
       <c r="J247" s="12" t="n"/>
+      <c r="K247" s="12" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="12" t="n"/>
@@ -4780,6 +4977,7 @@
       <c r="H248" s="12" t="n"/>
       <c r="I248" s="12" t="n"/>
       <c r="J248" s="12" t="n"/>
+      <c r="K248" s="12" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="12" t="n"/>
@@ -4792,6 +4990,7 @@
       <c r="H249" s="12" t="n"/>
       <c r="I249" s="12" t="n"/>
       <c r="J249" s="12" t="n"/>
+      <c r="K249" s="12" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="12" t="n"/>
@@ -4804,6 +5003,7 @@
       <c r="H250" s="12" t="n"/>
       <c r="I250" s="12" t="n"/>
       <c r="J250" s="12" t="n"/>
+      <c r="K250" s="12" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="12" t="n"/>
@@ -4816,6 +5016,7 @@
       <c r="H251" s="12" t="n"/>
       <c r="I251" s="12" t="n"/>
       <c r="J251" s="12" t="n"/>
+      <c r="K251" s="12" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="12" t="n"/>
@@ -4828,6 +5029,7 @@
       <c r="H252" s="12" t="n"/>
       <c r="I252" s="12" t="n"/>
       <c r="J252" s="12" t="n"/>
+      <c r="K252" s="12" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="12" t="n"/>
@@ -4840,6 +5042,7 @@
       <c r="H253" s="12" t="n"/>
       <c r="I253" s="12" t="n"/>
       <c r="J253" s="12" t="n"/>
+      <c r="K253" s="12" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="12" t="n"/>
@@ -4852,6 +5055,7 @@
       <c r="H254" s="12" t="n"/>
       <c r="I254" s="12" t="n"/>
       <c r="J254" s="12" t="n"/>
+      <c r="K254" s="12" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="12" t="n"/>
@@ -4864,6 +5068,7 @@
       <c r="H255" s="12" t="n"/>
       <c r="I255" s="12" t="n"/>
       <c r="J255" s="12" t="n"/>
+      <c r="K255" s="12" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="12" t="n"/>
@@ -4876,6 +5081,7 @@
       <c r="H256" s="12" t="n"/>
       <c r="I256" s="12" t="n"/>
       <c r="J256" s="12" t="n"/>
+      <c r="K256" s="12" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="12" t="n"/>
@@ -4888,6 +5094,7 @@
       <c r="H257" s="12" t="n"/>
       <c r="I257" s="12" t="n"/>
       <c r="J257" s="12" t="n"/>
+      <c r="K257" s="12" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="12" t="n"/>
@@ -4900,6 +5107,7 @@
       <c r="H258" s="12" t="n"/>
       <c r="I258" s="12" t="n"/>
       <c r="J258" s="12" t="n"/>
+      <c r="K258" s="12" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="12" t="n"/>
@@ -4912,6 +5120,7 @@
       <c r="H259" s="12" t="n"/>
       <c r="I259" s="12" t="n"/>
       <c r="J259" s="12" t="n"/>
+      <c r="K259" s="12" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="12" t="n"/>
@@ -4924,6 +5133,7 @@
       <c r="H260" s="12" t="n"/>
       <c r="I260" s="12" t="n"/>
       <c r="J260" s="12" t="n"/>
+      <c r="K260" s="12" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="12" t="n"/>
@@ -4936,6 +5146,7 @@
       <c r="H261" s="12" t="n"/>
       <c r="I261" s="12" t="n"/>
       <c r="J261" s="12" t="n"/>
+      <c r="K261" s="12" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="12" t="n"/>
@@ -4948,6 +5159,7 @@
       <c r="H262" s="12" t="n"/>
       <c r="I262" s="12" t="n"/>
       <c r="J262" s="12" t="n"/>
+      <c r="K262" s="12" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="12" t="n"/>
@@ -4960,6 +5172,7 @@
       <c r="H263" s="12" t="n"/>
       <c r="I263" s="12" t="n"/>
       <c r="J263" s="12" t="n"/>
+      <c r="K263" s="12" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="12" t="n"/>
@@ -4972,6 +5185,7 @@
       <c r="H264" s="12" t="n"/>
       <c r="I264" s="12" t="n"/>
       <c r="J264" s="12" t="n"/>
+      <c r="K264" s="12" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="12" t="n"/>
@@ -4984,6 +5198,7 @@
       <c r="H265" s="12" t="n"/>
       <c r="I265" s="12" t="n"/>
       <c r="J265" s="12" t="n"/>
+      <c r="K265" s="12" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="12" t="n"/>
@@ -4996,6 +5211,7 @@
       <c r="H266" s="12" t="n"/>
       <c r="I266" s="12" t="n"/>
       <c r="J266" s="12" t="n"/>
+      <c r="K266" s="12" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="12" t="n"/>
@@ -5008,6 +5224,7 @@
       <c r="H267" s="12" t="n"/>
       <c r="I267" s="12" t="n"/>
       <c r="J267" s="12" t="n"/>
+      <c r="K267" s="12" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="12" t="n"/>
@@ -5020,6 +5237,7 @@
       <c r="H268" s="12" t="n"/>
       <c r="I268" s="12" t="n"/>
       <c r="J268" s="12" t="n"/>
+      <c r="K268" s="12" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="12" t="n"/>
@@ -5032,6 +5250,7 @@
       <c r="H269" s="12" t="n"/>
       <c r="I269" s="12" t="n"/>
       <c r="J269" s="12" t="n"/>
+      <c r="K269" s="12" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="12" t="n"/>
@@ -5044,6 +5263,7 @@
       <c r="H270" s="12" t="n"/>
       <c r="I270" s="12" t="n"/>
       <c r="J270" s="12" t="n"/>
+      <c r="K270" s="12" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="12" t="n"/>
@@ -5056,6 +5276,7 @@
       <c r="H271" s="12" t="n"/>
       <c r="I271" s="12" t="n"/>
       <c r="J271" s="12" t="n"/>
+      <c r="K271" s="12" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="12" t="n"/>
@@ -5068,6 +5289,7 @@
       <c r="H272" s="12" t="n"/>
       <c r="I272" s="12" t="n"/>
       <c r="J272" s="12" t="n"/>
+      <c r="K272" s="12" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="12" t="n"/>
@@ -5080,6 +5302,7 @@
       <c r="H273" s="12" t="n"/>
       <c r="I273" s="12" t="n"/>
       <c r="J273" s="12" t="n"/>
+      <c r="K273" s="12" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="12" t="n"/>
@@ -5092,6 +5315,7 @@
       <c r="H274" s="12" t="n"/>
       <c r="I274" s="12" t="n"/>
       <c r="J274" s="12" t="n"/>
+      <c r="K274" s="12" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="12" t="n"/>
@@ -5104,6 +5328,7 @@
       <c r="H275" s="12" t="n"/>
       <c r="I275" s="12" t="n"/>
       <c r="J275" s="12" t="n"/>
+      <c r="K275" s="12" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="12" t="n"/>
@@ -5116,6 +5341,7 @@
       <c r="H276" s="12" t="n"/>
       <c r="I276" s="12" t="n"/>
       <c r="J276" s="12" t="n"/>
+      <c r="K276" s="12" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="2">

--- a/display/SimOutput_v2.xlsx
+++ b/display/SimOutput_v2.xlsx
@@ -2108,7 +2108,7 @@
       </c>
       <c r="K56" s="7" t="inlineStr">
         <is>
-          <t>ToF Tickets (cum)</t>
+          <t>ToF_Ticket_gains</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">

--- a/display/SimOutput_v2.xlsx
+++ b/display/SimOutput_v2.xlsx
@@ -1940,6 +1940,12 @@
           <t>-</t>
         </is>
       </c>
+      <c r="D46" s="11" t="inlineStr">
+        <is>
+          <t>ToF Tickets banked (this run)</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
@@ -1950,6 +1956,17 @@
       <c r="B47" s="8" t="inlineStr">
         <is>
           <t>-</t>
+        </is>
+      </c>
+      <c r="D47" s="11" t="inlineStr">
+        <is>
+          <t>ToF Tickets expected (mean)</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="n"/>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>the row above is ONE draw; this is the population mean EcoGainsSim carries. Tickets come in lumps of 2-6 on rungs that fire or do not, so a season can land at half or double the mean - Col_Cards_Cloud carries the p10-p90 band</t>
         </is>
       </c>
     </row>
